--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54198951-5D43-4E87-B969-C9B938A23257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96B1124-6013-4766-83A0-B1AE8C619E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,72 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>133973984</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  18.08.2025</t>
+  </si>
+  <si>
+    <t>133973941</t>
+  </si>
+  <si>
+    <t>133974844</t>
+  </si>
+  <si>
+    <t>133977272</t>
+  </si>
+  <si>
+    <t>133978756</t>
+  </si>
+  <si>
+    <t>133978866</t>
+  </si>
+  <si>
+    <t>133983112</t>
+  </si>
+  <si>
+    <t>133983270</t>
+  </si>
+  <si>
+    <t>133985970</t>
+  </si>
+  <si>
+    <t>133987741</t>
+  </si>
+  <si>
+    <t>133991021</t>
+  </si>
+  <si>
+    <t>133991543</t>
+  </si>
+  <si>
+    <t>133991495</t>
+  </si>
+  <si>
+    <t>133975597</t>
+  </si>
+  <si>
+    <t>133976492</t>
+  </si>
+  <si>
+    <t>133991842</t>
+  </si>
+  <si>
+    <t>133988778</t>
+  </si>
+  <si>
+    <t>133989292</t>
+  </si>
+  <si>
+    <t>133990125</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 18.08.2025</t>
   </si>
 </sst>
 </file>
@@ -486,100 +552,381 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F32"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96B1124-6013-4766-83A0-B1AE8C619E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABD9D77-6FFB-427A-ADDA-AD55BD16DE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,70 +51,94 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>133973984</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda  18.08.2025</t>
-  </si>
-  <si>
-    <t>133973941</t>
-  </si>
-  <si>
-    <t>133974844</t>
-  </si>
-  <si>
-    <t>133977272</t>
-  </si>
-  <si>
-    <t>133978756</t>
-  </si>
-  <si>
-    <t>133978866</t>
-  </si>
-  <si>
-    <t>133983112</t>
-  </si>
-  <si>
-    <t>133983270</t>
-  </si>
-  <si>
-    <t>133985970</t>
-  </si>
-  <si>
-    <t>133987741</t>
-  </si>
-  <si>
-    <t>133991021</t>
-  </si>
-  <si>
-    <t>133991543</t>
-  </si>
-  <si>
-    <t>133991495</t>
-  </si>
-  <si>
-    <t>133975597</t>
-  </si>
-  <si>
-    <t>133976492</t>
-  </si>
-  <si>
-    <t>133991842</t>
-  </si>
-  <si>
-    <t>133988778</t>
-  </si>
-  <si>
-    <t>133989292</t>
-  </si>
-  <si>
-    <t>133990125</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 18.08.2025</t>
+    <t>BLOQUEIOS HONDA 19.08.2025</t>
+  </si>
+  <si>
+    <t>133994395</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  19.08.2025</t>
+  </si>
+  <si>
+    <t>133994590</t>
+  </si>
+  <si>
+    <t>133994901</t>
+  </si>
+  <si>
+    <t>133995397</t>
+  </si>
+  <si>
+    <t>134002867</t>
+  </si>
+  <si>
+    <t>133996683</t>
+  </si>
+  <si>
+    <t>133997980</t>
+  </si>
+  <si>
+    <t>133997551</t>
+  </si>
+  <si>
+    <t>134001822</t>
+  </si>
+  <si>
+    <t>133999532</t>
+  </si>
+  <si>
+    <t>134001343</t>
+  </si>
+  <si>
+    <t>134001960</t>
+  </si>
+  <si>
+    <t>134002787</t>
+  </si>
+  <si>
+    <t>134002927</t>
+  </si>
+  <si>
+    <t>134005723</t>
+  </si>
+  <si>
+    <t>134005160</t>
+  </si>
+  <si>
+    <t>134010701</t>
+  </si>
+  <si>
+    <t>134007057</t>
+  </si>
+  <si>
+    <t>134005654</t>
+  </si>
+  <si>
+    <t>134006909</t>
+  </si>
+  <si>
+    <t>134009363</t>
+  </si>
+  <si>
+    <t>134009938</t>
+  </si>
+  <si>
+    <t>134010684</t>
+  </si>
+  <si>
+    <t>134010812</t>
+  </si>
+  <si>
+    <t>134011444</t>
+  </si>
+  <si>
+    <t>134016276</t>
+  </si>
+  <si>
+    <t>134014359</t>
   </si>
 </sst>
 </file>
@@ -553,16 +577,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -571,16 +595,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -589,16 +613,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -607,16 +631,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -625,16 +649,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -643,16 +667,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -661,16 +685,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -679,16 +703,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -697,16 +721,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -715,16 +739,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -733,16 +757,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -751,16 +775,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -769,16 +793,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -787,16 +811,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -805,16 +829,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -823,16 +847,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -841,16 +865,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -859,16 +883,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -877,16 +901,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -894,27 +918,147 @@
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABD9D77-6FFB-427A-ADDA-AD55BD16DE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0FF7C9-AAC4-4B71-BA14-B2AC30C00F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,85 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 19.08.2025</t>
-  </si>
-  <si>
-    <t>133994395</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  19.08.2025</t>
-  </si>
-  <si>
-    <t>133994590</t>
-  </si>
-  <si>
-    <t>133994901</t>
-  </si>
-  <si>
-    <t>133995397</t>
-  </si>
-  <si>
-    <t>134002867</t>
-  </si>
-  <si>
-    <t>133996683</t>
-  </si>
-  <si>
-    <t>133997980</t>
-  </si>
-  <si>
-    <t>133997551</t>
-  </si>
-  <si>
-    <t>134001822</t>
-  </si>
-  <si>
-    <t>133999532</t>
-  </si>
-  <si>
-    <t>134001343</t>
-  </si>
-  <si>
-    <t>134001960</t>
-  </si>
-  <si>
-    <t>134002787</t>
-  </si>
-  <si>
-    <t>134002927</t>
-  </si>
-  <si>
-    <t>134005723</t>
-  </si>
-  <si>
-    <t>134005160</t>
-  </si>
-  <si>
-    <t>134010701</t>
-  </si>
-  <si>
-    <t>134007057</t>
-  </si>
-  <si>
-    <t>134005654</t>
-  </si>
-  <si>
-    <t>134006909</t>
-  </si>
-  <si>
-    <t>134009363</t>
-  </si>
-  <si>
-    <t>134009938</t>
-  </si>
-  <si>
-    <t>134010684</t>
-  </si>
-  <si>
-    <t>134010812</t>
-  </si>
-  <si>
-    <t>134011444</t>
-  </si>
-  <si>
-    <t>134016276</t>
-  </si>
-  <si>
-    <t>134014359</t>
+    <t>134021458</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  20.08.2025</t>
+  </si>
+  <si>
+    <t>134022326</t>
+  </si>
+  <si>
+    <t>134023439</t>
+  </si>
+  <si>
+    <t>134025064</t>
+  </si>
+  <si>
+    <t>134025247</t>
+  </si>
+  <si>
+    <t>134025253</t>
+  </si>
+  <si>
+    <t>134025554</t>
+  </si>
+  <si>
+    <t>134026215</t>
+  </si>
+  <si>
+    <t>134028441</t>
+  </si>
+  <si>
+    <t>134028323</t>
+  </si>
+  <si>
+    <t>134031450</t>
+  </si>
+  <si>
+    <t>134037881</t>
+  </si>
+  <si>
+    <t>134034869</t>
+  </si>
+  <si>
+    <t>134036690</t>
+  </si>
+  <si>
+    <t>134038050</t>
+  </si>
+  <si>
+    <t>134038184</t>
+  </si>
+  <si>
+    <t>134038732</t>
+  </si>
+  <si>
+    <t>134021279</t>
+  </si>
+  <si>
+    <t>134023842</t>
+  </si>
+  <si>
+    <t>134023933</t>
+  </si>
+  <si>
+    <t>134027669</t>
+  </si>
+  <si>
+    <t>134028039</t>
+  </si>
+  <si>
+    <t>134031326</t>
+  </si>
+  <si>
+    <t>134032318</t>
+  </si>
+  <si>
+    <t>134033925</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 20.08.2025</t>
   </si>
 </sst>
 </file>
@@ -577,16 +571,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -595,16 +589,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -613,16 +607,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -631,16 +625,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -649,16 +643,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -667,16 +661,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -685,16 +679,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,16 +697,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -721,16 +715,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -739,16 +733,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -757,16 +751,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -775,16 +769,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -793,16 +787,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,16 +805,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -829,16 +823,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -847,16 +841,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -865,16 +859,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -883,16 +877,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -901,16 +895,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -919,16 +913,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -937,16 +931,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -955,16 +949,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -973,16 +967,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -991,16 +985,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1009,16 +1003,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1026,39 +1020,9 @@
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0FF7C9-AAC4-4B71-BA14-B2AC30C00F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1494446B-AB4C-4E41-90D2-EE24686B092B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="43">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,85 +54,109 @@
     <t>971</t>
   </si>
   <si>
-    <t>134021458</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  20.08.2025</t>
-  </si>
-  <si>
-    <t>134022326</t>
-  </si>
-  <si>
-    <t>134023439</t>
-  </si>
-  <si>
-    <t>134025064</t>
-  </si>
-  <si>
-    <t>134025247</t>
-  </si>
-  <si>
-    <t>134025253</t>
-  </si>
-  <si>
-    <t>134025554</t>
-  </si>
-  <si>
-    <t>134026215</t>
-  </si>
-  <si>
-    <t>134028441</t>
-  </si>
-  <si>
-    <t>134028323</t>
-  </si>
-  <si>
-    <t>134031450</t>
-  </si>
-  <si>
-    <t>134037881</t>
-  </si>
-  <si>
-    <t>134034869</t>
-  </si>
-  <si>
-    <t>134036690</t>
-  </si>
-  <si>
-    <t>134038050</t>
-  </si>
-  <si>
-    <t>134038184</t>
-  </si>
-  <si>
-    <t>134038732</t>
-  </si>
-  <si>
-    <t>134021279</t>
-  </si>
-  <si>
-    <t>134023842</t>
-  </si>
-  <si>
-    <t>134023933</t>
-  </si>
-  <si>
-    <t>134027669</t>
-  </si>
-  <si>
-    <t>134028039</t>
-  </si>
-  <si>
-    <t>134031326</t>
-  </si>
-  <si>
-    <t>134032318</t>
-  </si>
-  <si>
-    <t>134033925</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 20.08.2025</t>
+    <t>BLOQUEIOS HONDA 21.08.2025</t>
+  </si>
+  <si>
+    <t>134045101</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  21.08.2025</t>
+  </si>
+  <si>
+    <t>134041820</t>
+  </si>
+  <si>
+    <t>134043040</t>
+  </si>
+  <si>
+    <t>134045815</t>
+  </si>
+  <si>
+    <t>131619556</t>
+  </si>
+  <si>
+    <t>134054432</t>
+  </si>
+  <si>
+    <t>134043899</t>
+  </si>
+  <si>
+    <t>134044367</t>
+  </si>
+  <si>
+    <t>134045464</t>
+  </si>
+  <si>
+    <t>134050195</t>
+  </si>
+  <si>
+    <t>134045360</t>
+  </si>
+  <si>
+    <t>134046136</t>
+  </si>
+  <si>
+    <t>134046511</t>
+  </si>
+  <si>
+    <t>134048154</t>
+  </si>
+  <si>
+    <t>134048395</t>
+  </si>
+  <si>
+    <t>134049664</t>
+  </si>
+  <si>
+    <t>133687897</t>
+  </si>
+  <si>
+    <t>134053501</t>
+  </si>
+  <si>
+    <t>134052555</t>
+  </si>
+  <si>
+    <t>134053718</t>
+  </si>
+  <si>
+    <t>134055946</t>
+  </si>
+  <si>
+    <t>134057686</t>
+  </si>
+  <si>
+    <t>134057826</t>
+  </si>
+  <si>
+    <t>134057981</t>
+  </si>
+  <si>
+    <t>134059484</t>
+  </si>
+  <si>
+    <t>134059651</t>
+  </si>
+  <si>
+    <t>134060280</t>
+  </si>
+  <si>
+    <t>134060702</t>
+  </si>
+  <si>
+    <t>134061022</t>
+  </si>
+  <si>
+    <t>134051645</t>
+  </si>
+  <si>
+    <t>134057040</t>
+  </si>
+  <si>
+    <t>134058368</t>
+  </si>
+  <si>
+    <t>vBLOQUEIOS HONDA 21.08.2025</t>
   </si>
 </sst>
 </file>
@@ -571,16 +595,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,16 +613,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -607,16 +631,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -625,16 +649,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -643,16 +667,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -661,16 +685,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -679,16 +703,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -697,16 +721,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,16 +739,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -733,16 +757,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -751,16 +775,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,16 +793,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -787,16 +811,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,16 +829,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -823,16 +847,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -841,16 +865,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -859,16 +883,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -877,16 +901,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,16 +919,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,16 +937,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -931,16 +955,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -949,16 +973,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -967,16 +991,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -985,16 +1009,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1003,16 +1027,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1020,33 +1044,138 @@
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F36"/>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1494446B-AB4C-4E41-90D2-EE24686B092B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54942899-96A7-492D-9CF6-B29AFEE148B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="84">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,109 +54,232 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 21.08.2025</t>
-  </si>
-  <si>
-    <t>134045101</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  21.08.2025</t>
-  </si>
-  <si>
-    <t>134041820</t>
-  </si>
-  <si>
-    <t>134043040</t>
-  </si>
-  <si>
-    <t>134045815</t>
-  </si>
-  <si>
-    <t>131619556</t>
-  </si>
-  <si>
-    <t>134054432</t>
-  </si>
-  <si>
-    <t>134043899</t>
-  </si>
-  <si>
-    <t>134044367</t>
-  </si>
-  <si>
-    <t>134045464</t>
-  </si>
-  <si>
-    <t>134050195</t>
-  </si>
-  <si>
-    <t>134045360</t>
-  </si>
-  <si>
-    <t>134046136</t>
-  </si>
-  <si>
-    <t>134046511</t>
-  </si>
-  <si>
-    <t>134048154</t>
-  </si>
-  <si>
-    <t>134048395</t>
-  </si>
-  <si>
-    <t>134049664</t>
-  </si>
-  <si>
-    <t>133687897</t>
-  </si>
-  <si>
-    <t>134053501</t>
-  </si>
-  <si>
-    <t>134052555</t>
-  </si>
-  <si>
-    <t>134053718</t>
-  </si>
-  <si>
-    <t>134055946</t>
-  </si>
-  <si>
-    <t>134057686</t>
-  </si>
-  <si>
-    <t>134057826</t>
-  </si>
-  <si>
-    <t>134057981</t>
-  </si>
-  <si>
-    <t>134059484</t>
-  </si>
-  <si>
-    <t>134059651</t>
-  </si>
-  <si>
-    <t>134060280</t>
-  </si>
-  <si>
-    <t>134060702</t>
-  </si>
-  <si>
-    <t>134061022</t>
-  </si>
-  <si>
-    <t>134051645</t>
-  </si>
-  <si>
-    <t>134057040</t>
-  </si>
-  <si>
-    <t>134058368</t>
-  </si>
-  <si>
-    <t>vBLOQUEIOS HONDA 21.08.2025</t>
+    <t>134064447</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  22.08.2025</t>
+  </si>
+  <si>
+    <t>134065780</t>
+  </si>
+  <si>
+    <t>134076735</t>
+  </si>
+  <si>
+    <t>134064751</t>
+  </si>
+  <si>
+    <t>134064910</t>
+  </si>
+  <si>
+    <t>134065872</t>
+  </si>
+  <si>
+    <t>134065628</t>
+  </si>
+  <si>
+    <t>134069997</t>
+  </si>
+  <si>
+    <t>134070101</t>
+  </si>
+  <si>
+    <t>134070249</t>
+  </si>
+  <si>
+    <t>134070468</t>
+  </si>
+  <si>
+    <t>134070755</t>
+  </si>
+  <si>
+    <t>134072802</t>
+  </si>
+  <si>
+    <t>134071801</t>
+  </si>
+  <si>
+    <t>134072283</t>
+  </si>
+  <si>
+    <t>134072388</t>
+  </si>
+  <si>
+    <t>134072433</t>
+  </si>
+  <si>
+    <t>134084443</t>
+  </si>
+  <si>
+    <t>134075370</t>
+  </si>
+  <si>
+    <t>134076833</t>
+  </si>
+  <si>
+    <t>134078046</t>
+  </si>
+  <si>
+    <t>134079873</t>
+  </si>
+  <si>
+    <t>134078811</t>
+  </si>
+  <si>
+    <t>134079380</t>
+  </si>
+  <si>
+    <t>134079946</t>
+  </si>
+  <si>
+    <t>134080460</t>
+  </si>
+  <si>
+    <t>134082482</t>
+  </si>
+  <si>
+    <t>134083609</t>
+  </si>
+  <si>
+    <t>134085021</t>
+  </si>
+  <si>
+    <t>134085902</t>
+  </si>
+  <si>
+    <t>134086745</t>
+  </si>
+  <si>
+    <t>134066731</t>
+  </si>
+  <si>
+    <t>134070259</t>
+  </si>
+  <si>
+    <t>134075552</t>
+  </si>
+  <si>
+    <t>134077206</t>
+  </si>
+  <si>
+    <t>134077483</t>
+  </si>
+  <si>
+    <t>134079251</t>
+  </si>
+  <si>
+    <t>134080846</t>
+  </si>
+  <si>
+    <t>134088767</t>
+  </si>
+  <si>
+    <t>134088129</t>
+  </si>
+  <si>
+    <t>134088306</t>
+  </si>
+  <si>
+    <t>134088346</t>
+  </si>
+  <si>
+    <t>134088305</t>
+  </si>
+  <si>
+    <t>134088622</t>
+  </si>
+  <si>
+    <t>134089069</t>
+  </si>
+  <si>
+    <t>134089499</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2026</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2027</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2028</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2029</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2030</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2031</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2032</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2033</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2034</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2035</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2036</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2037</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2038</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2039</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2040</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2041</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2042</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2043</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2044</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2045</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2046</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2047</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2048</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2049</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2050</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2051</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.08.2052</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 23.08.2025</t>
   </si>
 </sst>
 </file>
@@ -563,7 +686,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -595,16 +718,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -613,16 +736,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -631,16 +754,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -649,16 +772,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -667,16 +790,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -685,16 +808,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -703,16 +826,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -721,16 +844,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -739,16 +862,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -757,16 +880,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -775,16 +898,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -793,16 +916,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -811,16 +934,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -829,16 +952,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -847,16 +970,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -865,16 +988,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -883,16 +1006,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -901,16 +1024,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -919,16 +1042,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -937,16 +1060,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -955,16 +1078,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -973,16 +1096,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -991,16 +1114,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1009,16 +1132,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1027,16 +1150,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1045,16 +1168,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1063,16 +1186,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1081,16 +1204,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1099,16 +1222,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1117,16 +1240,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1135,16 +1258,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1153,30 +1276,262 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54942899-96A7-492D-9CF6-B29AFEE148B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB009EAB-E28D-40ED-A7ED-32104EF76441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,12 +23,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="60">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,232 +65,160 @@
     <t>971</t>
   </si>
   <si>
-    <t>134064447</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  22.08.2025</t>
-  </si>
-  <si>
-    <t>134065780</t>
-  </si>
-  <si>
-    <t>134076735</t>
-  </si>
-  <si>
-    <t>134064751</t>
-  </si>
-  <si>
-    <t>134064910</t>
-  </si>
-  <si>
-    <t>134065872</t>
-  </si>
-  <si>
-    <t>134065628</t>
-  </si>
-  <si>
-    <t>134069997</t>
-  </si>
-  <si>
-    <t>134070101</t>
-  </si>
-  <si>
-    <t>134070249</t>
-  </si>
-  <si>
-    <t>134070468</t>
-  </si>
-  <si>
-    <t>134070755</t>
-  </si>
-  <si>
-    <t>134072802</t>
-  </si>
-  <si>
-    <t>134071801</t>
-  </si>
-  <si>
-    <t>134072283</t>
-  </si>
-  <si>
-    <t>134072388</t>
-  </si>
-  <si>
-    <t>134072433</t>
-  </si>
-  <si>
-    <t>134084443</t>
-  </si>
-  <si>
-    <t>134075370</t>
-  </si>
-  <si>
-    <t>134076833</t>
-  </si>
-  <si>
-    <t>134078046</t>
-  </si>
-  <si>
-    <t>134079873</t>
-  </si>
-  <si>
-    <t>134078811</t>
-  </si>
-  <si>
-    <t>134079380</t>
-  </si>
-  <si>
-    <t>134079946</t>
-  </si>
-  <si>
-    <t>134080460</t>
-  </si>
-  <si>
-    <t>134082482</t>
-  </si>
-  <si>
-    <t>134083609</t>
-  </si>
-  <si>
-    <t>134085021</t>
-  </si>
-  <si>
-    <t>134085902</t>
-  </si>
-  <si>
-    <t>134086745</t>
-  </si>
-  <si>
-    <t>134066731</t>
-  </si>
-  <si>
-    <t>134070259</t>
-  </si>
-  <si>
-    <t>134075552</t>
-  </si>
-  <si>
-    <t>134077206</t>
-  </si>
-  <si>
-    <t>134077483</t>
-  </si>
-  <si>
-    <t>134079251</t>
-  </si>
-  <si>
-    <t>134080846</t>
-  </si>
-  <si>
-    <t>134088767</t>
-  </si>
-  <si>
-    <t>134088129</t>
-  </si>
-  <si>
-    <t>134088306</t>
-  </si>
-  <si>
-    <t>134088346</t>
-  </si>
-  <si>
-    <t>134088305</t>
-  </si>
-  <si>
-    <t>134088622</t>
-  </si>
-  <si>
-    <t>134089069</t>
-  </si>
-  <si>
-    <t>134089499</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2026</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2027</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2028</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2029</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2030</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2031</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2032</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2033</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2034</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2035</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2036</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2037</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2038</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2039</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2040</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2041</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2042</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2043</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2044</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2045</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2046</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2047</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2048</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2049</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2050</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2051</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.08.2052</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 23.08.2025</t>
+    <t>134092682</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  25.08.2025</t>
+  </si>
+  <si>
+    <t>134092819</t>
+  </si>
+  <si>
+    <t>134092928</t>
+  </si>
+  <si>
+    <t>134093645</t>
+  </si>
+  <si>
+    <t>134093631</t>
+  </si>
+  <si>
+    <t>134094502</t>
+  </si>
+  <si>
+    <t>134095181</t>
+  </si>
+  <si>
+    <t>134110110</t>
+  </si>
+  <si>
+    <t>134101696</t>
+  </si>
+  <si>
+    <t>134097379</t>
+  </si>
+  <si>
+    <t>134096074</t>
+  </si>
+  <si>
+    <t>134099005</t>
+  </si>
+  <si>
+    <t>134109729</t>
+  </si>
+  <si>
+    <t>134099422</t>
+  </si>
+  <si>
+    <t>134100840</t>
+  </si>
+  <si>
+    <t>134101353</t>
+  </si>
+  <si>
+    <t>134102527</t>
+  </si>
+  <si>
+    <t>134103486</t>
+  </si>
+  <si>
+    <t>134103856</t>
+  </si>
+  <si>
+    <t>134106222</t>
+  </si>
+  <si>
+    <t>134107053</t>
+  </si>
+  <si>
+    <t>134110830</t>
+  </si>
+  <si>
+    <t>134111528</t>
+  </si>
+  <si>
+    <t>134110666</t>
+  </si>
+  <si>
+    <t>134110464</t>
+  </si>
+  <si>
+    <t>130779280</t>
+  </si>
+  <si>
+    <t>134110798</t>
+  </si>
+  <si>
+    <t>134111538</t>
+  </si>
+  <si>
+    <t>134107860</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2026</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2027</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2028</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2029</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2030</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2031</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2032</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2033</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2034</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2035</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2036</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2037</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2038</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2039</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2040</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2041</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2042</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2043</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2044</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2045</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.08.2046</t>
   </si>
 </sst>
 </file>
@@ -686,7 +625,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -727,7 +666,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -745,7 +684,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -763,7 +702,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -781,7 +720,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -799,7 +738,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -817,7 +756,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -835,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -853,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -871,7 +810,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -889,7 +828,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -907,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -925,7 +864,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -943,7 +882,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -961,7 +900,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -979,7 +918,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -997,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1015,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1033,7 +972,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1051,7 +990,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1069,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1087,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1105,7 +1044,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1123,7 +1062,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1141,7 +1080,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1159,7 +1098,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1177,7 +1116,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1195,7 +1134,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1213,7 +1152,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1231,307 +1170,12 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F30"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB009EAB-E28D-40ED-A7ED-32104EF76441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E536F22-E457-49BA-A213-BC2D54AC3DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -156,69 +156,6 @@
   </si>
   <si>
     <t>BLOQUEIOS HONDA 25.08.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2026</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2027</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2028</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2029</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2030</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2031</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2032</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2033</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2034</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2035</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2036</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2037</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2038</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2039</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2040</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2041</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2042</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2043</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2044</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2045</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2046</t>
   </si>
 </sst>
 </file>
@@ -810,7 +747,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -828,7 +765,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -846,7 +783,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -864,7 +801,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -882,7 +819,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -900,7 +837,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -918,7 +855,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -936,7 +873,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -954,7 +891,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -972,7 +909,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -990,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1008,7 +945,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1026,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1044,7 +981,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1062,7 +999,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1080,7 +1017,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1098,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1116,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1134,7 +1071,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1152,7 +1089,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1170,7 +1107,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E536F22-E457-49BA-A213-BC2D54AC3DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C5C691-364E-4C1B-8022-278D16C286B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="57">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -156,6 +156,60 @@
   </si>
   <si>
     <t>BLOQUEIOS HONDA 25.08.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 26.08.2025</t>
+  </si>
+  <si>
+    <t>134114434</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  26.08.2025</t>
+  </si>
+  <si>
+    <t>134114548</t>
+  </si>
+  <si>
+    <t>134116670</t>
+  </si>
+  <si>
+    <t>134124410</t>
+  </si>
+  <si>
+    <t>134129050</t>
+  </si>
+  <si>
+    <t>134122743</t>
+  </si>
+  <si>
+    <t>134128374</t>
+  </si>
+  <si>
+    <t>134130333</t>
+  </si>
+  <si>
+    <t>134132552</t>
+  </si>
+  <si>
+    <t>134136080</t>
+  </si>
+  <si>
+    <t>134117812</t>
+  </si>
+  <si>
+    <t>134118758</t>
+  </si>
+  <si>
+    <t>134119781</t>
+  </si>
+  <si>
+    <t>134130124</t>
+  </si>
+  <si>
+    <t>134133338</t>
+  </si>
+  <si>
+    <t>134134876</t>
   </si>
 </sst>
 </file>
@@ -562,7 +616,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -1113,6 +1167,278 @@
         <v>6</v>
       </c>
       <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C5C691-364E-4C1B-8022-278D16C286B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2115E5D-CE85-4371-BFC1-7F02092C6390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,151 +65,79 @@
     <t>971</t>
   </si>
   <si>
-    <t>134092682</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  25.08.2025</t>
-  </si>
-  <si>
-    <t>134092819</t>
-  </si>
-  <si>
-    <t>134092928</t>
-  </si>
-  <si>
-    <t>134093645</t>
-  </si>
-  <si>
-    <t>134093631</t>
-  </si>
-  <si>
-    <t>134094502</t>
-  </si>
-  <si>
-    <t>134095181</t>
-  </si>
-  <si>
-    <t>134110110</t>
-  </si>
-  <si>
-    <t>134101696</t>
-  </si>
-  <si>
-    <t>134097379</t>
-  </si>
-  <si>
-    <t>134096074</t>
-  </si>
-  <si>
-    <t>134099005</t>
-  </si>
-  <si>
-    <t>134109729</t>
-  </si>
-  <si>
-    <t>134099422</t>
-  </si>
-  <si>
-    <t>134100840</t>
-  </si>
-  <si>
-    <t>134101353</t>
-  </si>
-  <si>
-    <t>134102527</t>
-  </si>
-  <si>
-    <t>134103486</t>
-  </si>
-  <si>
-    <t>134103856</t>
-  </si>
-  <si>
-    <t>134106222</t>
-  </si>
-  <si>
-    <t>134107053</t>
-  </si>
-  <si>
-    <t>134110830</t>
-  </si>
-  <si>
-    <t>134111528</t>
-  </si>
-  <si>
-    <t>134110666</t>
-  </si>
-  <si>
-    <t>134110464</t>
-  </si>
-  <si>
-    <t>130779280</t>
-  </si>
-  <si>
-    <t>134110798</t>
-  </si>
-  <si>
-    <t>134111538</t>
-  </si>
-  <si>
-    <t>134107860</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 25.08.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 26.08.2025</t>
-  </si>
-  <si>
-    <t>134114434</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  26.08.2025</t>
-  </si>
-  <si>
-    <t>134114548</t>
-  </si>
-  <si>
-    <t>134116670</t>
-  </si>
-  <si>
-    <t>134124410</t>
-  </si>
-  <si>
-    <t>134129050</t>
-  </si>
-  <si>
-    <t>134122743</t>
-  </si>
-  <si>
-    <t>134128374</t>
-  </si>
-  <si>
-    <t>134130333</t>
-  </si>
-  <si>
-    <t>134132552</t>
-  </si>
-  <si>
-    <t>134136080</t>
-  </si>
-  <si>
-    <t>134117812</t>
-  </si>
-  <si>
-    <t>134118758</t>
-  </si>
-  <si>
-    <t>134119781</t>
-  </si>
-  <si>
-    <t>134130124</t>
-  </si>
-  <si>
-    <t>134133338</t>
-  </si>
-  <si>
-    <t>134134876</t>
+    <t>134138357</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  27.08.2025</t>
+  </si>
+  <si>
+    <t>134154650</t>
+  </si>
+  <si>
+    <t>134140450</t>
+  </si>
+  <si>
+    <t>134142328</t>
+  </si>
+  <si>
+    <t>134142398</t>
+  </si>
+  <si>
+    <t>134142374</t>
+  </si>
+  <si>
+    <t>134144331</t>
+  </si>
+  <si>
+    <t>134143826</t>
+  </si>
+  <si>
+    <t>134145121</t>
+  </si>
+  <si>
+    <t>134146425</t>
+  </si>
+  <si>
+    <t>134146411</t>
+  </si>
+  <si>
+    <t>134151092</t>
+  </si>
+  <si>
+    <t>134154311</t>
+  </si>
+  <si>
+    <t>134152472</t>
+  </si>
+  <si>
+    <t>134153633</t>
+  </si>
+  <si>
+    <t>134155121</t>
+  </si>
+  <si>
+    <t>134156010</t>
+  </si>
+  <si>
+    <t>134157245</t>
+  </si>
+  <si>
+    <t>134158743</t>
+  </si>
+  <si>
+    <t>134142347</t>
+  </si>
+  <si>
+    <t>134157648</t>
+  </si>
+  <si>
+    <t>134159114</t>
+  </si>
+  <si>
+    <t>134159224</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 27.08.2025</t>
   </si>
 </sst>
 </file>
@@ -616,7 +544,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -657,7 +585,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -675,7 +603,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -693,7 +621,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -711,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -729,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -747,7 +675,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -765,7 +693,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -783,7 +711,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -801,7 +729,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -819,7 +747,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -837,7 +765,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -855,7 +783,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -873,7 +801,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -891,7 +819,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -909,7 +837,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -927,7 +855,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -945,7 +873,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -963,7 +891,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -981,7 +909,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -999,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1017,7 +945,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1035,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1053,7 +981,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1061,384 +989,22 @@
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F30"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2115E5D-CE85-4371-BFC1-7F02092C6390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD3A786-1FF0-40A4-8A87-7BCDB05E61C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="28">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,79 +65,64 @@
     <t>971</t>
   </si>
   <si>
-    <t>134138357</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  27.08.2025</t>
-  </si>
-  <si>
-    <t>134154650</t>
-  </si>
-  <si>
-    <t>134140450</t>
-  </si>
-  <si>
-    <t>134142328</t>
-  </si>
-  <si>
-    <t>134142398</t>
-  </si>
-  <si>
-    <t>134142374</t>
-  </si>
-  <si>
-    <t>134144331</t>
-  </si>
-  <si>
-    <t>134143826</t>
-  </si>
-  <si>
-    <t>134145121</t>
-  </si>
-  <si>
-    <t>134146425</t>
-  </si>
-  <si>
-    <t>134146411</t>
-  </si>
-  <si>
-    <t>134151092</t>
-  </si>
-  <si>
-    <t>134154311</t>
-  </si>
-  <si>
-    <t>134152472</t>
-  </si>
-  <si>
-    <t>134153633</t>
-  </si>
-  <si>
-    <t>134155121</t>
-  </si>
-  <si>
-    <t>134156010</t>
-  </si>
-  <si>
-    <t>134157245</t>
-  </si>
-  <si>
-    <t>134158743</t>
-  </si>
-  <si>
-    <t>134142347</t>
-  </si>
-  <si>
-    <t>134157648</t>
-  </si>
-  <si>
-    <t>134159114</t>
-  </si>
-  <si>
-    <t>134159224</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 27.08.2025</t>
+    <t>BLOQUEIOS HONDA 28.08.2025</t>
+  </si>
+  <si>
+    <t>134166124</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  28.08.2025</t>
+  </si>
+  <si>
+    <t>134170950</t>
+  </si>
+  <si>
+    <t>134179946</t>
+  </si>
+  <si>
+    <t>134170806</t>
+  </si>
+  <si>
+    <t>134183454</t>
+  </si>
+  <si>
+    <t>134172184</t>
+  </si>
+  <si>
+    <t>134174391</t>
+  </si>
+  <si>
+    <t>134166336</t>
+  </si>
+  <si>
+    <t>134162340</t>
+  </si>
+  <si>
+    <t>134179381</t>
+  </si>
+  <si>
+    <t>134179699</t>
+  </si>
+  <si>
+    <t>131019167</t>
+  </si>
+  <si>
+    <t>134181642</t>
+  </si>
+  <si>
+    <t>134182660</t>
+  </si>
+  <si>
+    <t>134183386</t>
+  </si>
+  <si>
+    <t>134183404</t>
+  </si>
+  <si>
+    <t>134175413</t>
+  </si>
+  <si>
+    <t>134181577</t>
   </si>
 </sst>
 </file>
@@ -576,16 +561,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -594,16 +579,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -612,16 +597,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -630,16 +615,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -648,16 +633,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -666,16 +651,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -684,16 +669,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -702,16 +687,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -720,16 +705,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -738,16 +723,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -756,16 +741,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -774,16 +759,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -792,16 +777,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -810,16 +795,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -828,16 +813,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -846,16 +831,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -864,16 +849,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -882,16 +867,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -899,93 +884,18 @@
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD3A786-1FF0-40A4-8A87-7BCDB05E61C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35920116-B28C-4DC3-A1DC-B1D96106C2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="52">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,64 +65,136 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 28.08.2025</t>
-  </si>
-  <si>
-    <t>134166124</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  28.08.2025</t>
-  </si>
-  <si>
-    <t>134170950</t>
-  </si>
-  <si>
-    <t>134179946</t>
-  </si>
-  <si>
-    <t>134170806</t>
-  </si>
-  <si>
-    <t>134183454</t>
-  </si>
-  <si>
-    <t>134172184</t>
-  </si>
-  <si>
-    <t>134174391</t>
-  </si>
-  <si>
-    <t>134166336</t>
-  </si>
-  <si>
-    <t>134162340</t>
-  </si>
-  <si>
-    <t>134179381</t>
-  </si>
-  <si>
-    <t>134179699</t>
-  </si>
-  <si>
-    <t>131019167</t>
-  </si>
-  <si>
-    <t>134181642</t>
-  </si>
-  <si>
-    <t>134182660</t>
-  </si>
-  <si>
-    <t>134183386</t>
-  </si>
-  <si>
-    <t>134183404</t>
-  </si>
-  <si>
-    <t>134175413</t>
-  </si>
-  <si>
-    <t>134181577</t>
+    <t>134186260</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  29.08.2025</t>
+  </si>
+  <si>
+    <t>134187217</t>
+  </si>
+  <si>
+    <t>134187933</t>
+  </si>
+  <si>
+    <t>134199742</t>
+  </si>
+  <si>
+    <t>134188123</t>
+  </si>
+  <si>
+    <t>134189505</t>
+  </si>
+  <si>
+    <t>133872566</t>
+  </si>
+  <si>
+    <t>134192725</t>
+  </si>
+  <si>
+    <t>134193326</t>
+  </si>
+  <si>
+    <t>134192824</t>
+  </si>
+  <si>
+    <t>134195191</t>
+  </si>
+  <si>
+    <t>134195986</t>
+  </si>
+  <si>
+    <t>134196243</t>
+  </si>
+  <si>
+    <t>134200071</t>
+  </si>
+  <si>
+    <t>134200387</t>
+  </si>
+  <si>
+    <t>134201628</t>
+  </si>
+  <si>
+    <t>134201886</t>
+  </si>
+  <si>
+    <t>134204960</t>
+  </si>
+  <si>
+    <t>134206517</t>
+  </si>
+  <si>
+    <t>134206285</t>
+  </si>
+  <si>
+    <t>134206021</t>
+  </si>
+  <si>
+    <t>134206525</t>
+  </si>
+  <si>
+    <t>134206914</t>
+  </si>
+  <si>
+    <t>134208407</t>
+  </si>
+  <si>
+    <t>134207823</t>
+  </si>
+  <si>
+    <t>134186103</t>
+  </si>
+  <si>
+    <t>134193079</t>
+  </si>
+  <si>
+    <t>134192475</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 29.08.2025</t>
+  </si>
+  <si>
+    <t>134212563</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  30.08.2025</t>
+  </si>
+  <si>
+    <t>134212609</t>
+  </si>
+  <si>
+    <t>134211057</t>
+  </si>
+  <si>
+    <t>134211153</t>
+  </si>
+  <si>
+    <t>134211359</t>
+  </si>
+  <si>
+    <t>134212342</t>
+  </si>
+  <si>
+    <t>134211777</t>
+  </si>
+  <si>
+    <t>134211752</t>
+  </si>
+  <si>
+    <t>134211921</t>
+  </si>
+  <si>
+    <t>134211984</t>
+  </si>
+  <si>
+    <t>134212293</t>
+  </si>
+  <si>
+    <t>134212310</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 30.08.2025</t>
   </si>
 </sst>
 </file>
@@ -529,7 +601,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -561,16 +633,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -579,16 +651,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -597,16 +669,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -615,16 +687,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -633,16 +705,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -651,16 +723,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -669,16 +741,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -687,16 +759,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -705,16 +777,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -723,16 +795,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -741,16 +813,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -759,16 +831,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -777,16 +849,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -795,16 +867,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -813,16 +885,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -831,16 +903,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -849,16 +921,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -867,54 +939,406 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC62234E-9C72-4A98-A0B4-843394DD8C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045556CB-3C93-424D-9C8A-1B6ACFACCC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,43 +65,103 @@
     <t>971</t>
   </si>
   <si>
-    <t>Indexações Honda 01.09.25</t>
-  </si>
-  <si>
-    <t>134215974</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  01.09.2025</t>
-  </si>
-  <si>
-    <t>134217157</t>
-  </si>
-  <si>
-    <t>134219141</t>
-  </si>
-  <si>
-    <t>134221564</t>
-  </si>
-  <si>
-    <t>134221019</t>
-  </si>
-  <si>
-    <t>134221762</t>
-  </si>
-  <si>
-    <t>134224091</t>
-  </si>
-  <si>
-    <t>134225534</t>
-  </si>
-  <si>
-    <t>134231594</t>
-  </si>
-  <si>
-    <t>134232618</t>
-  </si>
-  <si>
-    <t>134232656</t>
+    <t>Indexações Honda 02.09.25</t>
+  </si>
+  <si>
+    <t>134234990</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  02.09.2025</t>
+  </si>
+  <si>
+    <t>134235265</t>
+  </si>
+  <si>
+    <t>134239370</t>
+  </si>
+  <si>
+    <t>134250909</t>
+  </si>
+  <si>
+    <t>134239875</t>
+  </si>
+  <si>
+    <t>134252695</t>
+  </si>
+  <si>
+    <t>134248151</t>
+  </si>
+  <si>
+    <t>134242970</t>
+  </si>
+  <si>
+    <t>134245709</t>
+  </si>
+  <si>
+    <t>134243829</t>
+  </si>
+  <si>
+    <t>134245065</t>
+  </si>
+  <si>
+    <t>134246542</t>
+  </si>
+  <si>
+    <t>134245188</t>
+  </si>
+  <si>
+    <t>134249351</t>
+  </si>
+  <si>
+    <t>134250174</t>
+  </si>
+  <si>
+    <t>134251640</t>
+  </si>
+  <si>
+    <t>134253253</t>
+  </si>
+  <si>
+    <t>134253850</t>
+  </si>
+  <si>
+    <t>134246656</t>
+  </si>
+  <si>
+    <t>134237343</t>
+  </si>
+  <si>
+    <t>134237638</t>
+  </si>
+  <si>
+    <t>134243671</t>
+  </si>
+  <si>
+    <t>134247717</t>
+  </si>
+  <si>
+    <t>134240984</t>
+  </si>
+  <si>
+    <t>134241711</t>
+  </si>
+  <si>
+    <t>134243269</t>
+  </si>
+  <si>
+    <t>134247229</t>
+  </si>
+  <si>
+    <t>134248095</t>
+  </si>
+  <si>
+    <t>134252144</t>
+  </si>
+  <si>
+    <t>134250084</t>
+  </si>
+  <si>
+    <t>134250754</t>
   </si>
 </sst>
 </file>
@@ -508,7 +568,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -735,6 +795,346 @@
         <v>6</v>
       </c>
       <c r="F12"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045556CB-3C93-424D-9C8A-1B6ACFACCC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA405164-8D49-4476-B1CD-A57ABD64F85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,103 +65,76 @@
     <t>971</t>
   </si>
   <si>
-    <t>Indexações Honda 02.09.25</t>
-  </si>
-  <si>
-    <t>134234990</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  02.09.2025</t>
-  </si>
-  <si>
-    <t>134235265</t>
-  </si>
-  <si>
-    <t>134239370</t>
-  </si>
-  <si>
-    <t>134250909</t>
-  </si>
-  <si>
-    <t>134239875</t>
-  </si>
-  <si>
-    <t>134252695</t>
-  </si>
-  <si>
-    <t>134248151</t>
-  </si>
-  <si>
-    <t>134242970</t>
-  </si>
-  <si>
-    <t>134245709</t>
-  </si>
-  <si>
-    <t>134243829</t>
-  </si>
-  <si>
-    <t>134245065</t>
-  </si>
-  <si>
-    <t>134246542</t>
-  </si>
-  <si>
-    <t>134245188</t>
-  </si>
-  <si>
-    <t>134249351</t>
-  </si>
-  <si>
-    <t>134250174</t>
-  </si>
-  <si>
-    <t>134251640</t>
-  </si>
-  <si>
-    <t>134253253</t>
-  </si>
-  <si>
-    <t>134253850</t>
-  </si>
-  <si>
-    <t>134246656</t>
-  </si>
-  <si>
-    <t>134237343</t>
-  </si>
-  <si>
-    <t>134237638</t>
-  </si>
-  <si>
-    <t>134243671</t>
-  </si>
-  <si>
-    <t>134247717</t>
-  </si>
-  <si>
-    <t>134240984</t>
-  </si>
-  <si>
-    <t>134241711</t>
-  </si>
-  <si>
-    <t>134243269</t>
-  </si>
-  <si>
-    <t>134247229</t>
-  </si>
-  <si>
-    <t>134248095</t>
-  </si>
-  <si>
-    <t>134252144</t>
-  </si>
-  <si>
-    <t>134250084</t>
-  </si>
-  <si>
-    <t>134250754</t>
+    <t>134260003</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  03.09.2025</t>
+  </si>
+  <si>
+    <t>134270080</t>
+  </si>
+  <si>
+    <t>134261198</t>
+  </si>
+  <si>
+    <t>134260055</t>
+  </si>
+  <si>
+    <t>134260848</t>
+  </si>
+  <si>
+    <t>134262771</t>
+  </si>
+  <si>
+    <t>134261721</t>
+  </si>
+  <si>
+    <t>134263748</t>
+  </si>
+  <si>
+    <t>134266450</t>
+  </si>
+  <si>
+    <t>134261922</t>
+  </si>
+  <si>
+    <t>134263812</t>
+  </si>
+  <si>
+    <t>134275571</t>
+  </si>
+  <si>
+    <t>134273362</t>
+  </si>
+  <si>
+    <t>134264384</t>
+  </si>
+  <si>
+    <t>134264654</t>
+  </si>
+  <si>
+    <t>134269930</t>
+  </si>
+  <si>
+    <t>134266606</t>
+  </si>
+  <si>
+    <t>134272028</t>
+  </si>
+  <si>
+    <t>134274371</t>
+  </si>
+  <si>
+    <t>134274405</t>
+  </si>
+  <si>
+    <t>134275529</t>
+  </si>
+  <si>
+    <t>134276150</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 03.09.2025</t>
   </si>
 </sst>
 </file>
@@ -568,7 +541,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -600,16 +573,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -618,16 +591,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -636,16 +609,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -654,16 +627,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -672,16 +645,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -690,16 +663,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -708,16 +681,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -726,16 +699,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -744,16 +717,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -762,16 +735,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -780,16 +753,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -798,16 +771,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -815,16 +788,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -832,16 +805,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -849,16 +822,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -866,16 +839,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -883,16 +856,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -900,16 +873,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -917,16 +890,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -934,16 +907,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -951,16 +924,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -968,171 +941,18 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA405164-8D49-4476-B1CD-A57ABD64F85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58051B3F-549B-4547-BC2A-D0BDDDDE115E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,76 +65,82 @@
     <t>971</t>
   </si>
   <si>
-    <t>134260003</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  03.09.2025</t>
-  </si>
-  <si>
-    <t>134270080</t>
-  </si>
-  <si>
-    <t>134261198</t>
-  </si>
-  <si>
-    <t>134260055</t>
-  </si>
-  <si>
-    <t>134260848</t>
-  </si>
-  <si>
-    <t>134262771</t>
-  </si>
-  <si>
-    <t>134261721</t>
-  </si>
-  <si>
-    <t>134263748</t>
-  </si>
-  <si>
-    <t>134266450</t>
-  </si>
-  <si>
-    <t>134261922</t>
-  </si>
-  <si>
-    <t>134263812</t>
-  </si>
-  <si>
-    <t>134275571</t>
-  </si>
-  <si>
-    <t>134273362</t>
-  </si>
-  <si>
-    <t>134264384</t>
-  </si>
-  <si>
-    <t>134264654</t>
-  </si>
-  <si>
-    <t>134269930</t>
-  </si>
-  <si>
-    <t>134266606</t>
-  </si>
-  <si>
-    <t>134272028</t>
-  </si>
-  <si>
-    <t>134274371</t>
-  </si>
-  <si>
-    <t>134274405</t>
-  </si>
-  <si>
-    <t>134275529</t>
-  </si>
-  <si>
-    <t>134276150</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 03.09.2025</t>
+    <t>BLOQUEIOS HONDA 04.09.2025</t>
+  </si>
+  <si>
+    <t>134280159</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  04.09.2025</t>
+  </si>
+  <si>
+    <t>134283826</t>
+  </si>
+  <si>
+    <t>134282503</t>
+  </si>
+  <si>
+    <t>134283115</t>
+  </si>
+  <si>
+    <t>134285041</t>
+  </si>
+  <si>
+    <t>133964421</t>
+  </si>
+  <si>
+    <t>134287039</t>
+  </si>
+  <si>
+    <t>134286893</t>
+  </si>
+  <si>
+    <t>134288613</t>
+  </si>
+  <si>
+    <t>134287529</t>
+  </si>
+  <si>
+    <t>134288479</t>
+  </si>
+  <si>
+    <t>134289009</t>
+  </si>
+  <si>
+    <t>134290896</t>
+  </si>
+  <si>
+    <t>134293170</t>
+  </si>
+  <si>
+    <t>134293455</t>
+  </si>
+  <si>
+    <t>134293769</t>
+  </si>
+  <si>
+    <t>134295787</t>
+  </si>
+  <si>
+    <t>134297637</t>
+  </si>
+  <si>
+    <t>134297592</t>
+  </si>
+  <si>
+    <t>134297869</t>
+  </si>
+  <si>
+    <t>134298303</t>
+  </si>
+  <si>
+    <t>134299074</t>
+  </si>
+  <si>
+    <t>134299153</t>
+  </si>
+  <si>
+    <t>134299373</t>
   </si>
 </sst>
 </file>
@@ -541,7 +547,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -573,16 +579,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -591,16 +597,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -609,16 +615,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -627,16 +633,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -645,16 +651,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -663,16 +669,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -681,16 +687,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -699,16 +705,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -717,16 +723,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -735,16 +741,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -753,16 +759,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -771,16 +777,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,16 +794,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,16 +811,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -822,16 +828,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -839,16 +845,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -856,16 +862,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -873,16 +879,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -890,16 +896,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -907,16 +913,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -924,16 +930,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -941,18 +947,52 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58051B3F-549B-4547-BC2A-D0BDDDDE115E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031EDD5F-D015-4101-A077-38187AE421A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,82 +65,139 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 04.09.2025</t>
-  </si>
-  <si>
-    <t>134280159</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  04.09.2025</t>
-  </si>
-  <si>
-    <t>134283826</t>
-  </si>
-  <si>
-    <t>134282503</t>
-  </si>
-  <si>
-    <t>134283115</t>
-  </si>
-  <si>
-    <t>134285041</t>
-  </si>
-  <si>
-    <t>133964421</t>
-  </si>
-  <si>
-    <t>134287039</t>
-  </si>
-  <si>
-    <t>134286893</t>
-  </si>
-  <si>
-    <t>134288613</t>
-  </si>
-  <si>
-    <t>134287529</t>
-  </si>
-  <si>
-    <t>134288479</t>
-  </si>
-  <si>
-    <t>134289009</t>
-  </si>
-  <si>
-    <t>134290896</t>
-  </si>
-  <si>
-    <t>134293170</t>
-  </si>
-  <si>
-    <t>134293455</t>
-  </si>
-  <si>
-    <t>134293769</t>
-  </si>
-  <si>
-    <t>134295787</t>
-  </si>
-  <si>
-    <t>134297637</t>
-  </si>
-  <si>
-    <t>134297592</t>
-  </si>
-  <si>
-    <t>134297869</t>
-  </si>
-  <si>
-    <t>134298303</t>
-  </si>
-  <si>
-    <t>134299074</t>
-  </si>
-  <si>
-    <t>134299153</t>
-  </si>
-  <si>
-    <t>134299373</t>
+    <t>134304472</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  05.09.2025</t>
+  </si>
+  <si>
+    <t>134305125</t>
+  </si>
+  <si>
+    <t>134308972</t>
+  </si>
+  <si>
+    <t>134309964</t>
+  </si>
+  <si>
+    <t>134310838</t>
+  </si>
+  <si>
+    <t>134317422</t>
+  </si>
+  <si>
+    <t>134312818</t>
+  </si>
+  <si>
+    <t>134313336</t>
+  </si>
+  <si>
+    <t>134315394</t>
+  </si>
+  <si>
+    <t>134316059</t>
+  </si>
+  <si>
+    <t>134316251</t>
+  </si>
+  <si>
+    <t>134316781</t>
+  </si>
+  <si>
+    <t>134318589</t>
+  </si>
+  <si>
+    <t>134321337</t>
+  </si>
+  <si>
+    <t>134320388</t>
+  </si>
+  <si>
+    <t>134322187</t>
+  </si>
+  <si>
+    <t>134323486</t>
+  </si>
+  <si>
+    <t>134322963</t>
+  </si>
+  <si>
+    <t>134323297</t>
+  </si>
+  <si>
+    <t>134323624</t>
+  </si>
+  <si>
+    <t>134303585</t>
+  </si>
+  <si>
+    <t>134303969</t>
+  </si>
+  <si>
+    <t>134306548</t>
+  </si>
+  <si>
+    <t>134306848</t>
+  </si>
+  <si>
+    <t>134313528</t>
+  </si>
+  <si>
+    <t>134307813</t>
+  </si>
+  <si>
+    <t>134318440</t>
+  </si>
+  <si>
+    <t>134321829</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 06.09.2025</t>
+  </si>
+  <si>
+    <t>134325785</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  06.09.2025</t>
+  </si>
+  <si>
+    <t>134325796</t>
+  </si>
+  <si>
+    <t>134326089</t>
+  </si>
+  <si>
+    <t>134326030</t>
+  </si>
+  <si>
+    <t>134326102</t>
+  </si>
+  <si>
+    <t>134326137</t>
+  </si>
+  <si>
+    <t>134326159</t>
+  </si>
+  <si>
+    <t>134326134</t>
+  </si>
+  <si>
+    <t>134326281</t>
+  </si>
+  <si>
+    <t>134326297</t>
+  </si>
+  <si>
+    <t>134326371</t>
+  </si>
+  <si>
+    <t>134326301</t>
+  </si>
+  <si>
+    <t>134326507</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 05.09.2025</t>
   </si>
 </sst>
 </file>
@@ -547,7 +604,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -579,16 +636,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -597,16 +654,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -615,16 +672,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -633,16 +690,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -651,16 +708,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -669,16 +726,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -687,16 +744,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -705,16 +762,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -723,16 +780,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -741,16 +798,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -759,16 +816,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -777,16 +834,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -794,16 +851,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,16 +868,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -828,16 +885,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,16 +902,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -862,16 +919,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -879,16 +936,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,16 +953,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,16 +970,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -930,16 +987,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -947,16 +1004,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -964,16 +1021,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -981,18 +1038,307 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031EDD5F-D015-4101-A077-38187AE421A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7163470D-40F5-446E-B710-3684155351FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -152,9 +152,6 @@
     <t>134321829</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 06.09.2025</t>
-  </si>
-  <si>
     <t>134325785</t>
   </si>
   <si>
@@ -197,7 +194,10 @@
     <t>134326507</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 05.09.2025</t>
+    <t>BLOQUEIOS HONDA 05.09.2025.xlsx</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 06.09.2025.xlsx</t>
   </si>
 </sst>
 </file>
@@ -645,7 +645,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -663,7 +663,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -681,7 +681,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -699,7 +699,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -717,7 +717,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -753,7 +753,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -771,7 +771,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -789,7 +789,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -825,7 +825,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -843,7 +843,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -860,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -894,7 +894,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -911,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -928,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -979,7 +979,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -996,7 +996,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1030,7 +1030,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1047,7 +1047,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1064,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1081,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1098,7 +1098,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1115,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1123,16 +1123,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1140,16 +1140,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1157,16 +1157,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1191,16 +1191,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1208,16 +1208,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1225,16 +1225,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1242,16 +1242,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1259,16 +1259,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1276,16 +1276,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1293,16 +1293,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1310,16 +1310,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1327,16 +1327,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7163470D-40F5-446E-B710-3684155351FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D56BCF1-BF7C-4412-8B27-9B63128BE1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="38">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -152,52 +152,7 @@
     <t>134321829</t>
   </si>
   <si>
-    <t>134325785</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  06.09.2025</t>
-  </si>
-  <si>
-    <t>134325796</t>
-  </si>
-  <si>
-    <t>134326089</t>
-  </si>
-  <si>
-    <t>134326030</t>
-  </si>
-  <si>
-    <t>134326102</t>
-  </si>
-  <si>
-    <t>134326137</t>
-  </si>
-  <si>
-    <t>134326159</t>
-  </si>
-  <si>
-    <t>134326134</t>
-  </si>
-  <si>
-    <t>134326281</t>
-  </si>
-  <si>
-    <t>134326297</t>
-  </si>
-  <si>
-    <t>134326371</t>
-  </si>
-  <si>
-    <t>134326301</t>
-  </si>
-  <si>
-    <t>134326507</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 05.09.2025.xlsx</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 06.09.2025.xlsx</t>
+    <t>BLOQUEIOS HONDA 05.09.2025</t>
   </si>
 </sst>
 </file>
@@ -604,7 +559,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -645,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -663,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -681,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -699,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -717,7 +672,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -735,7 +690,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -753,7 +708,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -771,7 +726,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -789,7 +744,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -807,7 +762,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -825,7 +780,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -843,7 +798,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -860,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -877,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -894,7 +849,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -911,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -928,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -945,7 +900,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -962,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -979,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -996,7 +951,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1030,7 +985,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1047,7 +1002,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1064,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1081,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1098,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1115,232 +1070,14 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D56BCF1-BF7C-4412-8B27-9B63128BE1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE810AB-8DD5-49F3-8046-5C14D7C6DCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,94 +65,94 @@
     <t>971</t>
   </si>
   <si>
-    <t>134304472</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  05.09.2025</t>
-  </si>
-  <si>
-    <t>134305125</t>
-  </si>
-  <si>
-    <t>134308972</t>
-  </si>
-  <si>
-    <t>134309964</t>
-  </si>
-  <si>
-    <t>134310838</t>
-  </si>
-  <si>
-    <t>134317422</t>
-  </si>
-  <si>
-    <t>134312818</t>
-  </si>
-  <si>
-    <t>134313336</t>
-  </si>
-  <si>
-    <t>134315394</t>
-  </si>
-  <si>
-    <t>134316059</t>
-  </si>
-  <si>
-    <t>134316251</t>
-  </si>
-  <si>
-    <t>134316781</t>
-  </si>
-  <si>
-    <t>134318589</t>
-  </si>
-  <si>
-    <t>134321337</t>
-  </si>
-  <si>
-    <t>134320388</t>
-  </si>
-  <si>
-    <t>134322187</t>
-  </si>
-  <si>
-    <t>134323486</t>
-  </si>
-  <si>
-    <t>134322963</t>
-  </si>
-  <si>
-    <t>134323297</t>
-  </si>
-  <si>
-    <t>134323624</t>
-  </si>
-  <si>
-    <t>134303585</t>
-  </si>
-  <si>
-    <t>134303969</t>
-  </si>
-  <si>
-    <t>134306548</t>
-  </si>
-  <si>
-    <t>134306848</t>
-  </si>
-  <si>
-    <t>134313528</t>
-  </si>
-  <si>
-    <t>134307813</t>
-  </si>
-  <si>
-    <t>134318440</t>
-  </si>
-  <si>
-    <t>134321829</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 05.09.2025</t>
+    <t>BLOQUEIOS HONDA 08.09.2025</t>
+  </si>
+  <si>
+    <t>134329762</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  08.09.2025</t>
+  </si>
+  <si>
+    <t>134333481</t>
+  </si>
+  <si>
+    <t>134329398</t>
+  </si>
+  <si>
+    <t>134329513</t>
+  </si>
+  <si>
+    <t>134329887</t>
+  </si>
+  <si>
+    <t>134330594</t>
+  </si>
+  <si>
+    <t>134330907</t>
+  </si>
+  <si>
+    <t>134331324</t>
+  </si>
+  <si>
+    <t>134340073</t>
+  </si>
+  <si>
+    <t>134332567</t>
+  </si>
+  <si>
+    <t>134332949</t>
+  </si>
+  <si>
+    <t>134333836</t>
+  </si>
+  <si>
+    <t>134335172</t>
+  </si>
+  <si>
+    <t>134334318</t>
+  </si>
+  <si>
+    <t>134336677</t>
+  </si>
+  <si>
+    <t>134338445</t>
+  </si>
+  <si>
+    <t>134341373</t>
+  </si>
+  <si>
+    <t>134341592</t>
+  </si>
+  <si>
+    <t>134343315</t>
+  </si>
+  <si>
+    <t>134343496</t>
+  </si>
+  <si>
+    <t>134344648</t>
+  </si>
+  <si>
+    <t>134345376</t>
+  </si>
+  <si>
+    <t>134345901</t>
+  </si>
+  <si>
+    <t>134346824</t>
+  </si>
+  <si>
+    <t>134329572</t>
+  </si>
+  <si>
+    <t>134329604</t>
+  </si>
+  <si>
+    <t>134330740</t>
+  </si>
+  <si>
+    <t>134335169</t>
   </si>
 </sst>
 </file>
@@ -591,16 +591,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -609,16 +609,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -627,16 +627,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -645,16 +645,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -663,16 +663,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -681,16 +681,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -717,16 +717,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -735,16 +735,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -753,16 +753,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -771,16 +771,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -789,16 +789,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -806,16 +806,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -823,16 +823,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -840,16 +840,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -857,16 +857,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -874,16 +874,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -891,16 +891,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -908,16 +908,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -925,16 +925,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -942,16 +942,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -959,16 +959,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -976,16 +976,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -993,16 +993,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1027,16 +1027,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1044,16 +1044,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1061,16 +1061,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE810AB-8DD5-49F3-8046-5C14D7C6DCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6E15A9-D533-425F-9E46-5264A839C7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,94 +65,76 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 08.09.2025</t>
-  </si>
-  <si>
-    <t>134329762</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  08.09.2025</t>
-  </si>
-  <si>
-    <t>134333481</t>
-  </si>
-  <si>
-    <t>134329398</t>
-  </si>
-  <si>
-    <t>134329513</t>
-  </si>
-  <si>
-    <t>134329887</t>
-  </si>
-  <si>
-    <t>134330594</t>
-  </si>
-  <si>
-    <t>134330907</t>
-  </si>
-  <si>
-    <t>134331324</t>
-  </si>
-  <si>
-    <t>134340073</t>
-  </si>
-  <si>
-    <t>134332567</t>
-  </si>
-  <si>
-    <t>134332949</t>
-  </si>
-  <si>
-    <t>134333836</t>
-  </si>
-  <si>
-    <t>134335172</t>
-  </si>
-  <si>
-    <t>134334318</t>
-  </si>
-  <si>
-    <t>134336677</t>
-  </si>
-  <si>
-    <t>134338445</t>
-  </si>
-  <si>
-    <t>134341373</t>
-  </si>
-  <si>
-    <t>134341592</t>
-  </si>
-  <si>
-    <t>134343315</t>
-  </si>
-  <si>
-    <t>134343496</t>
-  </si>
-  <si>
-    <t>134344648</t>
-  </si>
-  <si>
-    <t>134345376</t>
-  </si>
-  <si>
-    <t>134345901</t>
-  </si>
-  <si>
-    <t>134346824</t>
-  </si>
-  <si>
-    <t>134329572</t>
-  </si>
-  <si>
-    <t>134329604</t>
-  </si>
-  <si>
-    <t>134330740</t>
-  </si>
-  <si>
-    <t>134335169</t>
+    <t>Bloqueios Honda  09.09.2025</t>
+  </si>
+  <si>
+    <t>134349889</t>
+  </si>
+  <si>
+    <t>134354766</t>
+  </si>
+  <si>
+    <t>134351497</t>
+  </si>
+  <si>
+    <t>134351917</t>
+  </si>
+  <si>
+    <t>134365383</t>
+  </si>
+  <si>
+    <t>134353343</t>
+  </si>
+  <si>
+    <t>134356460</t>
+  </si>
+  <si>
+    <t>134355955</t>
+  </si>
+  <si>
+    <t>134356696</t>
+  </si>
+  <si>
+    <t>134358289</t>
+  </si>
+  <si>
+    <t>134357951</t>
+  </si>
+  <si>
+    <t>134360461</t>
+  </si>
+  <si>
+    <t>134369481</t>
+  </si>
+  <si>
+    <t>134366648</t>
+  </si>
+  <si>
+    <t>134366655</t>
+  </si>
+  <si>
+    <t>134367790</t>
+  </si>
+  <si>
+    <t>134368843</t>
+  </si>
+  <si>
+    <t>134368770</t>
+  </si>
+  <si>
+    <t>134369304</t>
+  </si>
+  <si>
+    <t>134369644</t>
+  </si>
+  <si>
+    <t>134352880</t>
+  </si>
+  <si>
+    <t>134369059</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 09.09.2025</t>
   </si>
 </sst>
 </file>
@@ -597,10 +579,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -609,16 +591,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -627,16 +609,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -645,16 +627,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -663,16 +645,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -681,16 +663,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -699,16 +681,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -717,16 +699,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -735,16 +717,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -753,16 +735,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -771,16 +753,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -789,16 +771,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -806,16 +788,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -823,16 +805,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -840,16 +822,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -857,16 +839,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -874,16 +856,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -891,16 +873,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -908,16 +890,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -925,16 +907,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -942,16 +924,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -959,120 +941,18 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6E15A9-D533-425F-9E46-5264A839C7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1694F201-3E19-4FE0-9D83-4576241BB192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,76 +65,118 @@
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda  09.09.2025</t>
-  </si>
-  <si>
-    <t>134349889</t>
-  </si>
-  <si>
-    <t>134354766</t>
-  </si>
-  <si>
-    <t>134351497</t>
-  </si>
-  <si>
-    <t>134351917</t>
-  </si>
-  <si>
-    <t>134365383</t>
-  </si>
-  <si>
-    <t>134353343</t>
-  </si>
-  <si>
-    <t>134356460</t>
-  </si>
-  <si>
-    <t>134355955</t>
-  </si>
-  <si>
-    <t>134356696</t>
-  </si>
-  <si>
-    <t>134358289</t>
-  </si>
-  <si>
-    <t>134357951</t>
-  </si>
-  <si>
-    <t>134360461</t>
-  </si>
-  <si>
-    <t>134369481</t>
-  </si>
-  <si>
-    <t>134366648</t>
-  </si>
-  <si>
-    <t>134366655</t>
-  </si>
-  <si>
-    <t>134367790</t>
-  </si>
-  <si>
-    <t>134368843</t>
-  </si>
-  <si>
-    <t>134368770</t>
-  </si>
-  <si>
-    <t>134369304</t>
-  </si>
-  <si>
-    <t>134369644</t>
-  </si>
-  <si>
-    <t>134352880</t>
-  </si>
-  <si>
-    <t>134369059</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 09.09.2025</t>
+    <t>BLOQUEIOS HONDA 10.09.2025</t>
+  </si>
+  <si>
+    <t>134374996</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  10.09.2025</t>
+  </si>
+  <si>
+    <t>134377560</t>
+  </si>
+  <si>
+    <t>134377162</t>
+  </si>
+  <si>
+    <t>134378215</t>
+  </si>
+  <si>
+    <t>134378387</t>
+  </si>
+  <si>
+    <t>134378936</t>
+  </si>
+  <si>
+    <t>134379274</t>
+  </si>
+  <si>
+    <t>134379671</t>
+  </si>
+  <si>
+    <t>134380102</t>
+  </si>
+  <si>
+    <t>134380585</t>
+  </si>
+  <si>
+    <t>134380670</t>
+  </si>
+  <si>
+    <t>134380676</t>
+  </si>
+  <si>
+    <t>133214788</t>
+  </si>
+  <si>
+    <t>134387231</t>
+  </si>
+  <si>
+    <t>134387260</t>
+  </si>
+  <si>
+    <t>134389874</t>
+  </si>
+  <si>
+    <t>134390480</t>
+  </si>
+  <si>
+    <t>134389850</t>
+  </si>
+  <si>
+    <t>134373697</t>
+  </si>
+  <si>
+    <t>134373252</t>
+  </si>
+  <si>
+    <t>134375117</t>
+  </si>
+  <si>
+    <t>134374804</t>
+  </si>
+  <si>
+    <t>134374739</t>
+  </si>
+  <si>
+    <t>134375496</t>
+  </si>
+  <si>
+    <t>134375673</t>
+  </si>
+  <si>
+    <t>134376403</t>
+  </si>
+  <si>
+    <t>134375971</t>
+  </si>
+  <si>
+    <t>134380372</t>
+  </si>
+  <si>
+    <t>134380749</t>
+  </si>
+  <si>
+    <t>134382105</t>
+  </si>
+  <si>
+    <t>134385264</t>
+  </si>
+  <si>
+    <t>134384663</t>
+  </si>
+  <si>
+    <t>134384504</t>
+  </si>
+  <si>
+    <t>134387710</t>
+  </si>
+  <si>
+    <t>134387671</t>
+  </si>
+  <si>
+    <t>134387693</t>
   </si>
 </sst>
 </file>
@@ -541,7 +583,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -579,10 +621,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -591,16 +633,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -609,16 +651,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -627,16 +669,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -645,16 +687,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -663,16 +705,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -681,16 +723,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -699,16 +741,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -717,16 +759,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -735,16 +777,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -753,16 +795,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -771,16 +813,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,16 +830,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,16 +847,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -822,16 +864,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -839,16 +881,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -856,16 +898,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -873,16 +915,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -890,16 +932,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -907,16 +949,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -924,16 +966,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -941,23 +983,258 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="6"/>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1694F201-3E19-4FE0-9D83-4576241BB192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397E0F8E-A832-4D05-AEB5-0B940ACEE7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,118 +65,79 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 10.09.2025</t>
-  </si>
-  <si>
-    <t>134374996</t>
-  </si>
-  <si>
     <t>Bloqueios Honda  10.09.2025</t>
   </si>
   <si>
-    <t>134377560</t>
-  </si>
-  <si>
-    <t>134377162</t>
-  </si>
-  <si>
-    <t>134378215</t>
-  </si>
-  <si>
-    <t>134378387</t>
-  </si>
-  <si>
-    <t>134378936</t>
-  </si>
-  <si>
-    <t>134379274</t>
-  </si>
-  <si>
-    <t>134379671</t>
-  </si>
-  <si>
-    <t>134380102</t>
-  </si>
-  <si>
-    <t>134380585</t>
-  </si>
-  <si>
-    <t>134380670</t>
-  </si>
-  <si>
-    <t>134380676</t>
-  </si>
-  <si>
-    <t>133214788</t>
-  </si>
-  <si>
-    <t>134387231</t>
-  </si>
-  <si>
-    <t>134387260</t>
-  </si>
-  <si>
-    <t>134389874</t>
-  </si>
-  <si>
-    <t>134390480</t>
-  </si>
-  <si>
-    <t>134389850</t>
-  </si>
-  <si>
-    <t>134373697</t>
-  </si>
-  <si>
-    <t>134373252</t>
-  </si>
-  <si>
-    <t>134375117</t>
-  </si>
-  <si>
-    <t>134374804</t>
-  </si>
-  <si>
-    <t>134374739</t>
-  </si>
-  <si>
-    <t>134375496</t>
-  </si>
-  <si>
-    <t>134375673</t>
-  </si>
-  <si>
-    <t>134376403</t>
-  </si>
-  <si>
-    <t>134375971</t>
-  </si>
-  <si>
-    <t>134380372</t>
-  </si>
-  <si>
-    <t>134380749</t>
-  </si>
-  <si>
-    <t>134382105</t>
-  </si>
-  <si>
-    <t>134385264</t>
-  </si>
-  <si>
-    <t>134384663</t>
-  </si>
-  <si>
-    <t>134384504</t>
-  </si>
-  <si>
-    <t>134387710</t>
-  </si>
-  <si>
-    <t>134387671</t>
-  </si>
-  <si>
-    <t>134387693</t>
+    <t>134399703</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  11.09.2025</t>
+  </si>
+  <si>
+    <t>134395524</t>
+  </si>
+  <si>
+    <t>134395984</t>
+  </si>
+  <si>
+    <t>134396014</t>
+  </si>
+  <si>
+    <t>134398366</t>
+  </si>
+  <si>
+    <t>134398202</t>
+  </si>
+  <si>
+    <t>134398326</t>
+  </si>
+  <si>
+    <t>134401505</t>
+  </si>
+  <si>
+    <t>134412243</t>
+  </si>
+  <si>
+    <t>132268563</t>
+  </si>
+  <si>
+    <t>134409155</t>
+  </si>
+  <si>
+    <t>134411778</t>
+  </si>
+  <si>
+    <t>134410814</t>
+  </si>
+  <si>
+    <t>134395118</t>
+  </si>
+  <si>
+    <t>134394894</t>
+  </si>
+  <si>
+    <t>134394478</t>
+  </si>
+  <si>
+    <t>133203892</t>
+  </si>
+  <si>
+    <t>134396090</t>
+  </si>
+  <si>
+    <t>134396765</t>
+  </si>
+  <si>
+    <t>134399648</t>
+  </si>
+  <si>
+    <t>134407762</t>
+  </si>
+  <si>
+    <t>134411079</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 11.09.2025</t>
   </si>
 </sst>
 </file>
@@ -583,7 +544,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -624,7 +585,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -639,10 +600,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -657,10 +618,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -675,10 +636,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -693,10 +654,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -714,7 +675,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -732,7 +693,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -750,7 +711,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -768,7 +729,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -786,7 +747,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -804,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -822,7 +783,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -839,7 +800,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -856,7 +817,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -873,7 +834,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -890,7 +851,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -907,7 +868,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -924,7 +885,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -941,7 +902,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -958,7 +919,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -975,7 +936,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -992,247 +953,9 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397E0F8E-A832-4D05-AEB5-0B940ACEE7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16797762-9883-4698-92EB-98F988C477D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="55">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -86,58 +86,124 @@
     <t>134398366</t>
   </si>
   <si>
-    <t>134398202</t>
-  </si>
-  <si>
-    <t>134398326</t>
-  </si>
-  <si>
-    <t>134401505</t>
-  </si>
-  <si>
-    <t>134412243</t>
-  </si>
-  <si>
-    <t>132268563</t>
-  </si>
-  <si>
-    <t>134409155</t>
-  </si>
-  <si>
-    <t>134411778</t>
-  </si>
-  <si>
-    <t>134410814</t>
-  </si>
-  <si>
-    <t>134395118</t>
-  </si>
-  <si>
-    <t>134394894</t>
-  </si>
-  <si>
-    <t>134394478</t>
-  </si>
-  <si>
-    <t>133203892</t>
-  </si>
-  <si>
-    <t>134396090</t>
-  </si>
-  <si>
-    <t>134396765</t>
-  </si>
-  <si>
-    <t>134399648</t>
-  </si>
-  <si>
-    <t>134407762</t>
-  </si>
-  <si>
-    <t>134411079</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 11.09.2025</t>
+    <t>134436396</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  12.09.2025</t>
+  </si>
+  <si>
+    <t>134435988</t>
+  </si>
+  <si>
+    <t>134420384</t>
+  </si>
+  <si>
+    <t>134418718</t>
+  </si>
+  <si>
+    <t>134420031</t>
+  </si>
+  <si>
+    <t>134420033</t>
+  </si>
+  <si>
+    <t>134422517</t>
+  </si>
+  <si>
+    <t>134423459</t>
+  </si>
+  <si>
+    <t>134426242</t>
+  </si>
+  <si>
+    <t>134426768</t>
+  </si>
+  <si>
+    <t>134429677</t>
+  </si>
+  <si>
+    <t>134430615</t>
+  </si>
+  <si>
+    <t>134431578</t>
+  </si>
+  <si>
+    <t>134431726</t>
+  </si>
+  <si>
+    <t>134432065</t>
+  </si>
+  <si>
+    <t>134432641</t>
+  </si>
+  <si>
+    <t>134433318</t>
+  </si>
+  <si>
+    <t>134433125</t>
+  </si>
+  <si>
+    <t>134433503</t>
+  </si>
+  <si>
+    <t>134434746</t>
+  </si>
+  <si>
+    <t>134433993</t>
+  </si>
+  <si>
+    <t>134434185</t>
+  </si>
+  <si>
+    <t>134435468</t>
+  </si>
+  <si>
+    <t>134437031</t>
+  </si>
+  <si>
+    <t>134437262</t>
+  </si>
+  <si>
+    <t>134437682</t>
+  </si>
+  <si>
+    <t>134438777</t>
+  </si>
+  <si>
+    <t>134424209</t>
+  </si>
+  <si>
+    <t>134417396</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 12.09.2025</t>
+  </si>
+  <si>
+    <t>134440177</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  13.09.2025</t>
+  </si>
+  <si>
+    <t>134440179</t>
+  </si>
+  <si>
+    <t>134440615</t>
+  </si>
+  <si>
+    <t>134440289</t>
+  </si>
+  <si>
+    <t>134440484</t>
+  </si>
+  <si>
+    <t>134440984</t>
+  </si>
+  <si>
+    <t>134440717</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 13.09.2025</t>
   </si>
 </sst>
 </file>
@@ -544,7 +610,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,9 +650,6 @@
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
@@ -602,9 +665,6 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
@@ -620,9 +680,6 @@
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
@@ -638,9 +695,6 @@
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
@@ -656,9 +710,6 @@
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
@@ -672,10 +723,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -684,16 +732,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -702,16 +747,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -720,16 +762,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -738,16 +777,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -756,16 +795,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -774,16 +813,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -791,16 +830,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -808,16 +847,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -825,16 +864,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -842,16 +881,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -859,16 +898,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -876,16 +915,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -893,16 +932,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -910,16 +949,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -927,16 +966,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -944,18 +983,426 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16797762-9883-4698-92EB-98F988C477D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716AED3F-C93E-492D-8894-7A96FDC28A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -56,9 +56,6 @@
     <t xml:space="preserve">Modelo/Descrição </t>
   </si>
   <si>
-    <t xml:space="preserve">Anexo </t>
-  </si>
-  <si>
     <t>Processar</t>
   </si>
   <si>
@@ -86,124 +83,79 @@
     <t>134398366</t>
   </si>
   <si>
-    <t>134436396</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  12.09.2025</t>
-  </si>
-  <si>
-    <t>134435988</t>
-  </si>
-  <si>
-    <t>134420384</t>
-  </si>
-  <si>
-    <t>134418718</t>
-  </si>
-  <si>
-    <t>134420031</t>
-  </si>
-  <si>
-    <t>134420033</t>
-  </si>
-  <si>
-    <t>134422517</t>
-  </si>
-  <si>
-    <t>134423459</t>
-  </si>
-  <si>
-    <t>134426242</t>
-  </si>
-  <si>
-    <t>134426768</t>
-  </si>
-  <si>
-    <t>134429677</t>
-  </si>
-  <si>
-    <t>134430615</t>
-  </si>
-  <si>
-    <t>134431578</t>
-  </si>
-  <si>
-    <t>134431726</t>
-  </si>
-  <si>
-    <t>134432065</t>
-  </si>
-  <si>
-    <t>134432641</t>
-  </si>
-  <si>
-    <t>134433318</t>
-  </si>
-  <si>
-    <t>134433125</t>
-  </si>
-  <si>
-    <t>134433503</t>
-  </si>
-  <si>
-    <t>134434746</t>
-  </si>
-  <si>
-    <t>134433993</t>
-  </si>
-  <si>
-    <t>134434185</t>
-  </si>
-  <si>
-    <t>134435468</t>
-  </si>
-  <si>
-    <t>134437031</t>
-  </si>
-  <si>
-    <t>134437262</t>
-  </si>
-  <si>
-    <t>134437682</t>
-  </si>
-  <si>
-    <t>134438777</t>
-  </si>
-  <si>
-    <t>134424209</t>
-  </si>
-  <si>
-    <t>134417396</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 12.09.2025</t>
-  </si>
-  <si>
-    <t>134440177</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  13.09.2025</t>
-  </si>
-  <si>
-    <t>134440179</t>
-  </si>
-  <si>
-    <t>134440615</t>
-  </si>
-  <si>
-    <t>134440289</t>
-  </si>
-  <si>
-    <t>134440484</t>
-  </si>
-  <si>
-    <t>134440984</t>
-  </si>
-  <si>
-    <t>134440717</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 13.09.2025</t>
+    <t>134443594</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  15.09.2025</t>
+  </si>
+  <si>
+    <t>134453680</t>
+  </si>
+  <si>
+    <t>134443820</t>
+  </si>
+  <si>
+    <t>134444121</t>
+  </si>
+  <si>
+    <t>134444834</t>
+  </si>
+  <si>
+    <t>134461400</t>
+  </si>
+  <si>
+    <t>134446456</t>
+  </si>
+  <si>
+    <t>134446729</t>
+  </si>
+  <si>
+    <t>134446523</t>
+  </si>
+  <si>
+    <t>134446745</t>
+  </si>
+  <si>
+    <t>134451922</t>
+  </si>
+  <si>
+    <t>134452746</t>
+  </si>
+  <si>
+    <t>134455764</t>
+  </si>
+  <si>
+    <t>134460328</t>
+  </si>
+  <si>
+    <t>134456345</t>
+  </si>
+  <si>
+    <t>134456623</t>
+  </si>
+  <si>
+    <t>134459867</t>
+  </si>
+  <si>
+    <t>134460947</t>
+  </si>
+  <si>
+    <t>134461131</t>
+  </si>
+  <si>
+    <t>134457027</t>
+  </si>
+  <si>
+    <t>134451880</t>
+  </si>
+  <si>
+    <t>132464419</t>
+  </si>
+  <si>
+    <t>134456742</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 15.09.2025</t>
   </si>
 </sst>
 </file>
@@ -610,7 +562,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -631,7 +583,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
@@ -642,768 +594,489 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
+      <c r="D3" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
+      <c r="D4" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
+      <c r="D5" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
+      <c r="D6" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716AED3F-C93E-492D-8894-7A96FDC28A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B4D2BD-E3D0-4BDD-A581-45B9BBD04448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -62,100 +62,85 @@
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda  10.09.2025</t>
-  </si>
-  <si>
-    <t>134399703</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  11.09.2025</t>
-  </si>
-  <si>
-    <t>134395524</t>
-  </si>
-  <si>
-    <t>134395984</t>
-  </si>
-  <si>
-    <t>134396014</t>
-  </si>
-  <si>
-    <t>134398366</t>
-  </si>
-  <si>
-    <t>134443594</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  15.09.2025</t>
-  </si>
-  <si>
-    <t>134453680</t>
-  </si>
-  <si>
-    <t>134443820</t>
-  </si>
-  <si>
-    <t>134444121</t>
-  </si>
-  <si>
-    <t>134444834</t>
-  </si>
-  <si>
-    <t>134461400</t>
-  </si>
-  <si>
-    <t>134446456</t>
-  </si>
-  <si>
-    <t>134446729</t>
-  </si>
-  <si>
-    <t>134446523</t>
-  </si>
-  <si>
-    <t>134446745</t>
-  </si>
-  <si>
-    <t>134451922</t>
-  </si>
-  <si>
-    <t>134452746</t>
-  </si>
-  <si>
-    <t>134455764</t>
-  </si>
-  <si>
-    <t>134460328</t>
-  </si>
-  <si>
-    <t>134456345</t>
-  </si>
-  <si>
-    <t>134456623</t>
-  </si>
-  <si>
-    <t>134459867</t>
-  </si>
-  <si>
-    <t>134460947</t>
-  </si>
-  <si>
-    <t>134461131</t>
-  </si>
-  <si>
-    <t>134457027</t>
-  </si>
-  <si>
-    <t>134451880</t>
-  </si>
-  <si>
-    <t>132464419</t>
-  </si>
-  <si>
-    <t>134456742</t>
-  </si>
-  <si>
     <t>BLOQUEIOS HONDA 15.09.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 16.09.2025</t>
+  </si>
+  <si>
+    <t>134487028</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  16.09.2025</t>
+  </si>
+  <si>
+    <t>134465562</t>
+  </si>
+  <si>
+    <t>134466346</t>
+  </si>
+  <si>
+    <t>134468886</t>
+  </si>
+  <si>
+    <t>134468287</t>
+  </si>
+  <si>
+    <t>134481494</t>
+  </si>
+  <si>
+    <t>134472971</t>
+  </si>
+  <si>
+    <t>134474114</t>
+  </si>
+  <si>
+    <t>134474345</t>
+  </si>
+  <si>
+    <t>134474626</t>
+  </si>
+  <si>
+    <t>134476858</t>
+  </si>
+  <si>
+    <t>134478482</t>
+  </si>
+  <si>
+    <t>134478312</t>
+  </si>
+  <si>
+    <t>134478472</t>
+  </si>
+  <si>
+    <t>134479374</t>
+  </si>
+  <si>
+    <t>134480984</t>
+  </si>
+  <si>
+    <t>134484372</t>
+  </si>
+  <si>
+    <t>134483225</t>
+  </si>
+  <si>
+    <t>134485103</t>
+  </si>
+  <si>
+    <t>134485252</t>
+  </si>
+  <si>
+    <t>134485410</t>
+  </si>
+  <si>
+    <t>134465464</t>
+  </si>
+  <si>
+    <t>134471554</t>
+  </si>
+  <si>
+    <t>134479039</t>
   </si>
 </sst>
 </file>
@@ -562,7 +547,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -583,7 +568,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
@@ -594,16 +579,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -612,16 +597,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -630,16 +615,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -648,16 +633,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -666,16 +651,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -684,16 +669,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -708,10 +693,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -726,10 +711,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -744,10 +729,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -762,10 +747,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -780,10 +765,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -798,10 +783,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -815,10 +800,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -832,10 +817,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -849,10 +834,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -866,10 +851,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -883,10 +868,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -900,10 +885,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -917,10 +902,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -934,10 +919,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -951,10 +936,10 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -968,10 +953,10 @@
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -985,10 +970,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -1002,80 +987,12 @@
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B4D2BD-E3D0-4BDD-A581-45B9BBD04448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313A97A8-FD61-40C7-8A37-0A3608BF40C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,82 +65,82 @@
     <t>BLOQUEIOS HONDA 15.09.2025</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 16.09.2025</t>
-  </si>
-  <si>
-    <t>134487028</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  16.09.2025</t>
-  </si>
-  <si>
-    <t>134465562</t>
-  </si>
-  <si>
-    <t>134466346</t>
-  </si>
-  <si>
-    <t>134468886</t>
-  </si>
-  <si>
-    <t>134468287</t>
-  </si>
-  <si>
-    <t>134481494</t>
-  </si>
-  <si>
-    <t>134472971</t>
-  </si>
-  <si>
-    <t>134474114</t>
-  </si>
-  <si>
-    <t>134474345</t>
-  </si>
-  <si>
-    <t>134474626</t>
-  </si>
-  <si>
-    <t>134476858</t>
-  </si>
-  <si>
-    <t>134478482</t>
-  </si>
-  <si>
-    <t>134478312</t>
-  </si>
-  <si>
-    <t>134478472</t>
-  </si>
-  <si>
-    <t>134479374</t>
-  </si>
-  <si>
-    <t>134480984</t>
-  </si>
-  <si>
-    <t>134484372</t>
-  </si>
-  <si>
-    <t>134483225</t>
-  </si>
-  <si>
-    <t>134485103</t>
-  </si>
-  <si>
-    <t>134485252</t>
-  </si>
-  <si>
-    <t>134485410</t>
-  </si>
-  <si>
-    <t>134465464</t>
-  </si>
-  <si>
-    <t>134471554</t>
-  </si>
-  <si>
-    <t>134479039</t>
+    <t>BLOQUEIOS HONDA 17.09.2025</t>
+  </si>
+  <si>
+    <t>134505550</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  17.09.2025</t>
+  </si>
+  <si>
+    <t>134489288</t>
+  </si>
+  <si>
+    <t>134488789</t>
+  </si>
+  <si>
+    <t>134489065</t>
+  </si>
+  <si>
+    <t>134489010</t>
+  </si>
+  <si>
+    <t>134489560</t>
+  </si>
+  <si>
+    <t>130599549</t>
+  </si>
+  <si>
+    <t>134497785</t>
+  </si>
+  <si>
+    <t>134495169</t>
+  </si>
+  <si>
+    <t>134494832</t>
+  </si>
+  <si>
+    <t>134496168</t>
+  </si>
+  <si>
+    <t>134496634</t>
+  </si>
+  <si>
+    <t>134496794</t>
+  </si>
+  <si>
+    <t>134497205</t>
+  </si>
+  <si>
+    <t>134498233</t>
+  </si>
+  <si>
+    <t>134499912</t>
+  </si>
+  <si>
+    <t>134502469</t>
+  </si>
+  <si>
+    <t>134505960</t>
+  </si>
+  <si>
+    <t>134506499</t>
+  </si>
+  <si>
+    <t>134508084</t>
+  </si>
+  <si>
+    <t>134507437</t>
+  </si>
+  <si>
+    <t>134508360</t>
+  </si>
+  <si>
+    <t>134508532</t>
+  </si>
+  <si>
+    <t>134509150</t>
   </si>
 </sst>
 </file>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313A97A8-FD61-40C7-8A37-0A3608BF40C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70DEB95-ED71-4842-91C1-9225DB1FE6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,82 +65,67 @@
     <t>BLOQUEIOS HONDA 15.09.2025</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 17.09.2025</t>
-  </si>
-  <si>
-    <t>134505550</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  17.09.2025</t>
-  </si>
-  <si>
-    <t>134489288</t>
-  </si>
-  <si>
-    <t>134488789</t>
-  </si>
-  <si>
-    <t>134489065</t>
-  </si>
-  <si>
-    <t>134489010</t>
-  </si>
-  <si>
-    <t>134489560</t>
-  </si>
-  <si>
-    <t>130599549</t>
-  </si>
-  <si>
-    <t>134497785</t>
-  </si>
-  <si>
-    <t>134495169</t>
-  </si>
-  <si>
-    <t>134494832</t>
-  </si>
-  <si>
-    <t>134496168</t>
-  </si>
-  <si>
-    <t>134496634</t>
-  </si>
-  <si>
-    <t>134496794</t>
-  </si>
-  <si>
-    <t>134497205</t>
-  </si>
-  <si>
-    <t>134498233</t>
-  </si>
-  <si>
-    <t>134499912</t>
-  </si>
-  <si>
-    <t>134502469</t>
-  </si>
-  <si>
-    <t>134505960</t>
-  </si>
-  <si>
-    <t>134506499</t>
-  </si>
-  <si>
-    <t>134508084</t>
-  </si>
-  <si>
-    <t>134507437</t>
-  </si>
-  <si>
-    <t>134508360</t>
-  </si>
-  <si>
-    <t>134508532</t>
-  </si>
-  <si>
-    <t>134509150</t>
+    <t>BLOQUEIOS HONDA 18.09.2025</t>
+  </si>
+  <si>
+    <t>134512207</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  18.09.2025</t>
+  </si>
+  <si>
+    <t>134512715</t>
+  </si>
+  <si>
+    <t>134513689</t>
+  </si>
+  <si>
+    <t>134514475</t>
+  </si>
+  <si>
+    <t>134520203</t>
+  </si>
+  <si>
+    <t>134515493</t>
+  </si>
+  <si>
+    <t>134516389</t>
+  </si>
+  <si>
+    <t>134516356</t>
+  </si>
+  <si>
+    <t>134516358</t>
+  </si>
+  <si>
+    <t>134518744</t>
+  </si>
+  <si>
+    <t>132172852</t>
+  </si>
+  <si>
+    <t>134525439</t>
+  </si>
+  <si>
+    <t>134527813</t>
+  </si>
+  <si>
+    <t>134526993</t>
+  </si>
+  <si>
+    <t>134527175</t>
+  </si>
+  <si>
+    <t>134527087</t>
+  </si>
+  <si>
+    <t>134527298</t>
+  </si>
+  <si>
+    <t>134530459</t>
+  </si>
+  <si>
+    <t>134530717</t>
   </si>
 </sst>
 </file>
@@ -547,7 +532,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -908,91 +893,6 @@
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70DEB95-ED71-4842-91C1-9225DB1FE6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7B45C5-B43D-4C46-90CB-635ED1291F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,67 +65,103 @@
     <t>BLOQUEIOS HONDA 15.09.2025</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 18.09.2025</t>
-  </si>
-  <si>
-    <t>134512207</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  18.09.2025</t>
-  </si>
-  <si>
-    <t>134512715</t>
-  </si>
-  <si>
-    <t>134513689</t>
-  </si>
-  <si>
-    <t>134514475</t>
-  </si>
-  <si>
-    <t>134520203</t>
-  </si>
-  <si>
-    <t>134515493</t>
-  </si>
-  <si>
-    <t>134516389</t>
-  </si>
-  <si>
-    <t>134516356</t>
-  </si>
-  <si>
-    <t>134516358</t>
-  </si>
-  <si>
-    <t>134518744</t>
-  </si>
-  <si>
-    <t>132172852</t>
-  </si>
-  <si>
-    <t>134525439</t>
-  </si>
-  <si>
-    <t>134527813</t>
-  </si>
-  <si>
-    <t>134526993</t>
-  </si>
-  <si>
-    <t>134527175</t>
-  </si>
-  <si>
-    <t>134527087</t>
-  </si>
-  <si>
-    <t>134527298</t>
-  </si>
-  <si>
-    <t>134530459</t>
-  </si>
-  <si>
-    <t>134530717</t>
+    <t>134542453</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 19.09.2025</t>
+  </si>
+  <si>
+    <t>134550990</t>
+  </si>
+  <si>
+    <t>134538042</t>
+  </si>
+  <si>
+    <t>134538329</t>
+  </si>
+  <si>
+    <t>134543636</t>
+  </si>
+  <si>
+    <t>134542809</t>
+  </si>
+  <si>
+    <t>134544114</t>
+  </si>
+  <si>
+    <t>134544168</t>
+  </si>
+  <si>
+    <t>134544193</t>
+  </si>
+  <si>
+    <t>134554560</t>
+  </si>
+  <si>
+    <t>134546611</t>
+  </si>
+  <si>
+    <t>134546164</t>
+  </si>
+  <si>
+    <t>134546399</t>
+  </si>
+  <si>
+    <t>134539912</t>
+  </si>
+  <si>
+    <t>134549941</t>
+  </si>
+  <si>
+    <t>134549245</t>
+  </si>
+  <si>
+    <t>134554356</t>
+  </si>
+  <si>
+    <t>134555374</t>
+  </si>
+  <si>
+    <t>134556728</t>
+  </si>
+  <si>
+    <t>134533747</t>
+  </si>
+  <si>
+    <t>134534257</t>
+  </si>
+  <si>
+    <t>134537370</t>
+  </si>
+  <si>
+    <t>134537674</t>
+  </si>
+  <si>
+    <t>134540388</t>
+  </si>
+  <si>
+    <t>134541994</t>
+  </si>
+  <si>
+    <t>134547299</t>
+  </si>
+  <si>
+    <t>134551002</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 19.09.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 20.09.2025</t>
+  </si>
+  <si>
+    <t>134558749</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 20.09.2025</t>
+  </si>
+  <si>
+    <t>134558911</t>
   </si>
 </sst>
 </file>
@@ -532,7 +568,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -564,16 +600,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -582,16 +618,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -600,16 +636,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -618,16 +654,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -636,16 +672,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -654,16 +690,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -672,16 +708,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -690,16 +726,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -708,16 +744,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -726,16 +762,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -744,16 +780,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -762,16 +798,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -779,16 +815,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -796,16 +832,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -813,16 +849,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -830,16 +866,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -847,16 +883,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -864,16 +900,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -881,18 +917,188 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7B45C5-B43D-4C46-90CB-635ED1291F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3389654-6583-450C-A0C1-F53AE3135069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,103 +65,58 @@
     <t>BLOQUEIOS HONDA 15.09.2025</t>
   </si>
   <si>
-    <t>134542453</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 19.09.2025</t>
-  </si>
-  <si>
-    <t>134550990</t>
-  </si>
-  <si>
-    <t>134538042</t>
-  </si>
-  <si>
-    <t>134538329</t>
-  </si>
-  <si>
-    <t>134543636</t>
-  </si>
-  <si>
-    <t>134542809</t>
-  </si>
-  <si>
-    <t>134544114</t>
-  </si>
-  <si>
-    <t>134544168</t>
-  </si>
-  <si>
-    <t>134544193</t>
-  </si>
-  <si>
-    <t>134554560</t>
-  </si>
-  <si>
-    <t>134546611</t>
-  </si>
-  <si>
-    <t>134546164</t>
-  </si>
-  <si>
-    <t>134546399</t>
-  </si>
-  <si>
-    <t>134539912</t>
-  </si>
-  <si>
-    <t>134549941</t>
-  </si>
-  <si>
-    <t>134549245</t>
-  </si>
-  <si>
-    <t>134554356</t>
-  </si>
-  <si>
-    <t>134555374</t>
-  </si>
-  <si>
-    <t>134556728</t>
-  </si>
-  <si>
-    <t>134533747</t>
-  </si>
-  <si>
-    <t>134534257</t>
-  </si>
-  <si>
-    <t>134537370</t>
-  </si>
-  <si>
-    <t>134537674</t>
-  </si>
-  <si>
-    <t>134540388</t>
-  </si>
-  <si>
-    <t>134541994</t>
-  </si>
-  <si>
-    <t>134547299</t>
-  </si>
-  <si>
-    <t>134551002</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 19.09.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 20.09.2025</t>
-  </si>
-  <si>
-    <t>134558749</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 20.09.2025</t>
-  </si>
-  <si>
-    <t>134558911</t>
+    <t>BLOQUEIOS HONDA 22.09.2025</t>
+  </si>
+  <si>
+    <t>134570793</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 22.09.2025</t>
+  </si>
+  <si>
+    <t>134562464</t>
+  </si>
+  <si>
+    <t>134564940</t>
+  </si>
+  <si>
+    <t>134566051</t>
+  </si>
+  <si>
+    <t>134574905</t>
+  </si>
+  <si>
+    <t>134569847</t>
+  </si>
+  <si>
+    <t>134571518</t>
+  </si>
+  <si>
+    <t>134574394</t>
+  </si>
+  <si>
+    <t>134574952</t>
+  </si>
+  <si>
+    <t>134575213</t>
+  </si>
+  <si>
+    <t>134575724</t>
+  </si>
+  <si>
+    <t>134579384</t>
+  </si>
+  <si>
+    <t>134579745</t>
+  </si>
+  <si>
+    <t>134581091</t>
+  </si>
+  <si>
+    <t>134578047</t>
+  </si>
+  <si>
+    <t>134578490</t>
   </si>
 </sst>
 </file>
@@ -568,7 +523,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -600,16 +555,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -618,16 +573,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -636,16 +591,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -654,16 +609,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -672,16 +627,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -690,16 +645,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -708,16 +663,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -726,16 +681,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -744,16 +699,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -762,16 +717,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -780,16 +735,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -798,16 +753,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -815,16 +770,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -832,16 +787,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -849,16 +804,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -866,239 +821,18 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3389654-6583-450C-A0C1-F53AE3135069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06965CBC-3131-4D30-ACFC-029B219EF323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,58 +65,58 @@
     <t>BLOQUEIOS HONDA 15.09.2025</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 22.09.2025</t>
-  </si>
-  <si>
-    <t>134570793</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 22.09.2025</t>
-  </si>
-  <si>
-    <t>134562464</t>
-  </si>
-  <si>
-    <t>134564940</t>
-  </si>
-  <si>
-    <t>134566051</t>
-  </si>
-  <si>
-    <t>134574905</t>
-  </si>
-  <si>
-    <t>134569847</t>
-  </si>
-  <si>
-    <t>134571518</t>
-  </si>
-  <si>
-    <t>134574394</t>
-  </si>
-  <si>
-    <t>134574952</t>
-  </si>
-  <si>
-    <t>134575213</t>
-  </si>
-  <si>
-    <t>134575724</t>
-  </si>
-  <si>
-    <t>134579384</t>
-  </si>
-  <si>
-    <t>134579745</t>
-  </si>
-  <si>
-    <t>134581091</t>
-  </si>
-  <si>
-    <t>134578047</t>
-  </si>
-  <si>
-    <t>134578490</t>
+    <t>BLOQUEIOS HONDA 23.09.2025</t>
+  </si>
+  <si>
+    <t>134586386</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 23.09.2025</t>
+  </si>
+  <si>
+    <t>134585981</t>
+  </si>
+  <si>
+    <t>134590230</t>
+  </si>
+  <si>
+    <t>134590228</t>
+  </si>
+  <si>
+    <t>134590588</t>
+  </si>
+  <si>
+    <t>134592009</t>
+  </si>
+  <si>
+    <t>134592241</t>
+  </si>
+  <si>
+    <t>134599180</t>
+  </si>
+  <si>
+    <t>134602111</t>
+  </si>
+  <si>
+    <t>134602938</t>
+  </si>
+  <si>
+    <t>134589316</t>
+  </si>
+  <si>
+    <t>134593147</t>
+  </si>
+  <si>
+    <t>134595677</t>
+  </si>
+  <si>
+    <t>134596096</t>
+  </si>
+  <si>
+    <t>130903484</t>
+  </si>
+  <si>
+    <t>134598444</t>
   </si>
 </sst>
 </file>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06965CBC-3131-4D30-ACFC-029B219EF323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A4AAD0-B826-4DE5-BA81-C4166EA74D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="22">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -62,61 +62,49 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 15.09.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 23.09.2025</t>
-  </si>
-  <si>
-    <t>134586386</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 23.09.2025</t>
-  </si>
-  <si>
-    <t>134585981</t>
-  </si>
-  <si>
-    <t>134590230</t>
-  </si>
-  <si>
-    <t>134590228</t>
-  </si>
-  <si>
-    <t>134590588</t>
-  </si>
-  <si>
-    <t>134592009</t>
-  </si>
-  <si>
-    <t>134592241</t>
-  </si>
-  <si>
-    <t>134599180</t>
-  </si>
-  <si>
-    <t>134602111</t>
-  </si>
-  <si>
-    <t>134602938</t>
-  </si>
-  <si>
-    <t>134589316</t>
-  </si>
-  <si>
-    <t>134593147</t>
-  </si>
-  <si>
-    <t>134595677</t>
-  </si>
-  <si>
-    <t>134596096</t>
-  </si>
-  <si>
-    <t>130903484</t>
-  </si>
-  <si>
-    <t>134598444</t>
+    <t>BLOQUEIOS HONDA 24.09.2025</t>
+  </si>
+  <si>
+    <t>134609093</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 24.09.2025</t>
+  </si>
+  <si>
+    <t>134615510</t>
+  </si>
+  <si>
+    <t>134611735</t>
+  </si>
+  <si>
+    <t>134613566</t>
+  </si>
+  <si>
+    <t>134621850</t>
+  </si>
+  <si>
+    <t>134611341</t>
+  </si>
+  <si>
+    <t>134625020</t>
+  </si>
+  <si>
+    <t>134617997</t>
+  </si>
+  <si>
+    <t>134618986</t>
+  </si>
+  <si>
+    <t>134616273</t>
+  </si>
+  <si>
+    <t>134621037</t>
+  </si>
+  <si>
+    <t>134622674</t>
+  </si>
+  <si>
+    <t>134623586</t>
   </si>
 </sst>
 </file>
@@ -523,7 +511,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -555,16 +543,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -573,16 +561,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -591,16 +579,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -609,16 +597,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -627,16 +615,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -645,16 +633,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -663,16 +651,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -681,16 +669,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -699,16 +687,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -717,16 +705,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -735,16 +723,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -753,16 +741,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -770,69 +758,18 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A4AAD0-B826-4DE5-BA81-C4166EA74D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABFDBD3-DDB1-44A7-93E3-3BEC96448E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,46 +65,79 @@
     <t>BLOQUEIOS HONDA 24.09.2025</t>
   </si>
   <si>
-    <t>134609093</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 24.09.2025</t>
-  </si>
-  <si>
-    <t>134615510</t>
-  </si>
-  <si>
-    <t>134611735</t>
-  </si>
-  <si>
-    <t>134613566</t>
-  </si>
-  <si>
-    <t>134621850</t>
-  </si>
-  <si>
-    <t>134611341</t>
-  </si>
-  <si>
-    <t>134625020</t>
-  </si>
-  <si>
-    <t>134617997</t>
-  </si>
-  <si>
-    <t>134618986</t>
-  </si>
-  <si>
-    <t>134616273</t>
-  </si>
-  <si>
-    <t>134621037</t>
-  </si>
-  <si>
-    <t>134622674</t>
-  </si>
-  <si>
-    <t>134623586</t>
+    <t>134790091</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 06.10.2025</t>
+  </si>
+  <si>
+    <t>134791291</t>
+  </si>
+  <si>
+    <t>134795117</t>
+  </si>
+  <si>
+    <t>134791134</t>
+  </si>
+  <si>
+    <t>134792311</t>
+  </si>
+  <si>
+    <t>134793594</t>
+  </si>
+  <si>
+    <t>134793657</t>
+  </si>
+  <si>
+    <t>134796008</t>
+  </si>
+  <si>
+    <t>134796701</t>
+  </si>
+  <si>
+    <t>134798789</t>
+  </si>
+  <si>
+    <t>134797036</t>
+  </si>
+  <si>
+    <t>134797375</t>
+  </si>
+  <si>
+    <t>134799875</t>
+  </si>
+  <si>
+    <t>134803097</t>
+  </si>
+  <si>
+    <t>134804771</t>
+  </si>
+  <si>
+    <t>134805533</t>
+  </si>
+  <si>
+    <t>134802905</t>
+  </si>
+  <si>
+    <t>134798050</t>
+  </si>
+  <si>
+    <t>134798970</t>
+  </si>
+  <si>
+    <t>134800461</t>
+  </si>
+  <si>
+    <t>134803457</t>
+  </si>
+  <si>
+    <t>134804791</t>
+  </si>
+  <si>
+    <t>134805878</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 06.10.2025</t>
   </si>
 </sst>
 </file>
@@ -511,7 +544,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -552,7 +585,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -570,7 +603,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -588,7 +621,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -606,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -624,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -642,7 +675,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -660,7 +693,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -678,7 +711,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -696,7 +729,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -714,7 +747,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -732,7 +765,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -750,7 +783,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -767,9 +800,179 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -787,31 +990,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABFDBD3-DDB1-44A7-93E3-3BEC96448E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BD51FB-6495-480F-80EF-831818925E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,15 +59,18 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>BLOQUEIOS HONDA 24.09.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 06.10.2025</t>
+  </si>
+  <si>
+    <t>134790091</t>
+  </si>
+  <si>
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 24.09.2025</t>
-  </si>
-  <si>
-    <t>134790091</t>
-  </si>
-  <si>
     <t>Bloqueios Honda 06.10.2025</t>
   </si>
   <si>
@@ -135,9 +138,6 @@
   </si>
   <si>
     <t>134805878</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 06.10.2025</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
@@ -579,13 +579,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -594,16 +594,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -612,16 +612,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -630,16 +630,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -648,16 +648,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -666,16 +666,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -684,16 +684,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -702,16 +702,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -720,16 +720,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -738,16 +738,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -756,16 +756,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -774,16 +774,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -791,16 +791,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -808,16 +808,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -825,16 +825,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -842,16 +842,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -859,16 +859,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -876,16 +876,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -893,16 +893,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -910,16 +910,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -944,16 +944,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -961,16 +961,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BD51FB-6495-480F-80EF-831818925E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84619ADE-CF9E-4AE9-AEF1-80C3E4A0255C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -62,82 +62,55 @@
     <t>BLOQUEIOS HONDA 24.09.2025</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 06.10.2025</t>
-  </si>
-  <si>
-    <t>134790091</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 06.10.2025</t>
-  </si>
-  <si>
-    <t>134791291</t>
-  </si>
-  <si>
-    <t>134795117</t>
-  </si>
-  <si>
-    <t>134791134</t>
-  </si>
-  <si>
-    <t>134792311</t>
-  </si>
-  <si>
-    <t>134793594</t>
-  </si>
-  <si>
-    <t>134793657</t>
-  </si>
-  <si>
-    <t>134796008</t>
-  </si>
-  <si>
-    <t>134796701</t>
-  </si>
-  <si>
-    <t>134798789</t>
-  </si>
-  <si>
-    <t>134797036</t>
-  </si>
-  <si>
-    <t>134797375</t>
-  </si>
-  <si>
-    <t>134799875</t>
-  </si>
-  <si>
-    <t>134803097</t>
-  </si>
-  <si>
-    <t>134804771</t>
-  </si>
-  <si>
-    <t>134805533</t>
-  </si>
-  <si>
-    <t>134802905</t>
-  </si>
-  <si>
-    <t>134798050</t>
-  </si>
-  <si>
-    <t>134798970</t>
-  </si>
-  <si>
-    <t>134800461</t>
-  </si>
-  <si>
-    <t>134803457</t>
-  </si>
-  <si>
-    <t>134804791</t>
-  </si>
-  <si>
-    <t>134805878</t>
+    <t>134810873</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 07.10.2025</t>
+  </si>
+  <si>
+    <t>134811463</t>
+  </si>
+  <si>
+    <t>134811627</t>
+  </si>
+  <si>
+    <t>134812122</t>
+  </si>
+  <si>
+    <t>134815536</t>
+  </si>
+  <si>
+    <t>134816289</t>
+  </si>
+  <si>
+    <t>134818715</t>
+  </si>
+  <si>
+    <t>134819364</t>
+  </si>
+  <si>
+    <t>134825211</t>
+  </si>
+  <si>
+    <t>134827591</t>
+  </si>
+  <si>
+    <t>134826981</t>
+  </si>
+  <si>
+    <t>134827573</t>
+  </si>
+  <si>
+    <t>134828602</t>
+  </si>
+  <si>
+    <t>134826810</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 07.10.2025</t>
   </si>
 </sst>
 </file>
@@ -544,7 +517,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -579,13 +552,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -594,16 +567,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -612,16 +585,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -630,16 +603,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -648,16 +621,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -666,16 +639,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -684,16 +657,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -702,16 +675,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -720,16 +693,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -738,16 +711,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -756,16 +729,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -774,16 +747,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -791,16 +764,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -808,171 +781,18 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -990,31 +810,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84619ADE-CF9E-4AE9-AEF1-80C3E4A0255C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99D67C9-93C6-4659-8896-55FD46BEDFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -810,31 +810,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99D67C9-93C6-4659-8896-55FD46BEDFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11311677-5845-4DA2-912F-DCDC81EC1E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,52 +65,82 @@
     <t>971</t>
   </si>
   <si>
-    <t>134810873</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 07.10.2025</t>
-  </si>
-  <si>
-    <t>134811463</t>
-  </si>
-  <si>
-    <t>134811627</t>
-  </si>
-  <si>
-    <t>134812122</t>
-  </si>
-  <si>
-    <t>134815536</t>
-  </si>
-  <si>
-    <t>134816289</t>
-  </si>
-  <si>
-    <t>134818715</t>
-  </si>
-  <si>
-    <t>134819364</t>
-  </si>
-  <si>
-    <t>134825211</t>
-  </si>
-  <si>
-    <t>134827591</t>
-  </si>
-  <si>
-    <t>134826981</t>
-  </si>
-  <si>
-    <t>134827573</t>
-  </si>
-  <si>
-    <t>134828602</t>
-  </si>
-  <si>
-    <t>134826810</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 07.10.2025</t>
+    <t>BLOQUEIOS HONDA 09.10.2025</t>
+  </si>
+  <si>
+    <t>134852540</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 09.10.2025</t>
+  </si>
+  <si>
+    <t>134852964</t>
+  </si>
+  <si>
+    <t>133168738</t>
+  </si>
+  <si>
+    <t>134854308</t>
+  </si>
+  <si>
+    <t>134854750</t>
+  </si>
+  <si>
+    <t>134855775</t>
+  </si>
+  <si>
+    <t>134857615</t>
+  </si>
+  <si>
+    <t>134859670</t>
+  </si>
+  <si>
+    <t>134859446</t>
+  </si>
+  <si>
+    <t>134859754</t>
+  </si>
+  <si>
+    <t>134860022</t>
+  </si>
+  <si>
+    <t>134861482</t>
+  </si>
+  <si>
+    <t>134863007</t>
+  </si>
+  <si>
+    <t>134863822</t>
+  </si>
+  <si>
+    <t>134864841</t>
+  </si>
+  <si>
+    <t>134864708</t>
+  </si>
+  <si>
+    <t>134866143</t>
+  </si>
+  <si>
+    <t>134867686</t>
+  </si>
+  <si>
+    <t>134866813</t>
+  </si>
+  <si>
+    <t>134867647</t>
+  </si>
+  <si>
+    <t>134869375</t>
+  </si>
+  <si>
+    <t>134868816</t>
+  </si>
+  <si>
+    <t>134869363</t>
+  </si>
+  <si>
+    <t>134863994</t>
   </si>
 </sst>
 </file>
@@ -517,7 +547,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -549,16 +579,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -567,16 +597,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -585,16 +615,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -603,16 +633,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -621,16 +651,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -639,16 +669,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -657,16 +687,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -675,16 +705,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -693,16 +723,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -711,16 +741,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -729,16 +759,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -747,16 +777,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -764,16 +794,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -781,18 +811,188 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -810,31 +1010,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11311677-5845-4DA2-912F-DCDC81EC1E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E2731-8597-4FBE-96B9-CCB1E1A10ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,82 +65,118 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 09.10.2025</t>
-  </si>
-  <si>
-    <t>134852540</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 09.10.2025</t>
-  </si>
-  <si>
-    <t>134852964</t>
-  </si>
-  <si>
-    <t>133168738</t>
-  </si>
-  <si>
-    <t>134854308</t>
-  </si>
-  <si>
-    <t>134854750</t>
-  </si>
-  <si>
-    <t>134855775</t>
-  </si>
-  <si>
-    <t>134857615</t>
-  </si>
-  <si>
-    <t>134859670</t>
-  </si>
-  <si>
-    <t>134859446</t>
-  </si>
-  <si>
-    <t>134859754</t>
-  </si>
-  <si>
-    <t>134860022</t>
-  </si>
-  <si>
-    <t>134861482</t>
-  </si>
-  <si>
-    <t>134863007</t>
-  </si>
-  <si>
-    <t>134863822</t>
-  </si>
-  <si>
-    <t>134864841</t>
-  </si>
-  <si>
-    <t>134864708</t>
-  </si>
-  <si>
-    <t>134866143</t>
-  </si>
-  <si>
-    <t>134867686</t>
-  </si>
-  <si>
-    <t>134866813</t>
-  </si>
-  <si>
-    <t>134867647</t>
-  </si>
-  <si>
-    <t>134869375</t>
-  </si>
-  <si>
-    <t>134868816</t>
-  </si>
-  <si>
-    <t>134869363</t>
-  </si>
-  <si>
-    <t>134863994</t>
+    <t>BLOQUEIOS HONDA 10.10.2025</t>
+  </si>
+  <si>
+    <t>134873797</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 10.10.2025</t>
+  </si>
+  <si>
+    <t>134874162</t>
+  </si>
+  <si>
+    <t>134877198</t>
+  </si>
+  <si>
+    <t>134878394</t>
+  </si>
+  <si>
+    <t>134879442</t>
+  </si>
+  <si>
+    <t>134879919</t>
+  </si>
+  <si>
+    <t>134880048</t>
+  </si>
+  <si>
+    <t>134881500</t>
+  </si>
+  <si>
+    <t>134888999</t>
+  </si>
+  <si>
+    <t>134885230</t>
+  </si>
+  <si>
+    <t>134886317</t>
+  </si>
+  <si>
+    <t>134891167</t>
+  </si>
+  <si>
+    <t>134888267</t>
+  </si>
+  <si>
+    <t>134892347</t>
+  </si>
+  <si>
+    <t>134889893</t>
+  </si>
+  <si>
+    <t>134889595</t>
+  </si>
+  <si>
+    <t>134891290</t>
+  </si>
+  <si>
+    <t>134890153</t>
+  </si>
+  <si>
+    <t>134893153</t>
+  </si>
+  <si>
+    <t>134873786</t>
+  </si>
+  <si>
+    <t>134873890</t>
+  </si>
+  <si>
+    <t>134874875</t>
+  </si>
+  <si>
+    <t>134883895</t>
+  </si>
+  <si>
+    <t>134895479</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 11.10.2025</t>
+  </si>
+  <si>
+    <t>134895584</t>
+  </si>
+  <si>
+    <t>134895652</t>
+  </si>
+  <si>
+    <t>134895603</t>
+  </si>
+  <si>
+    <t>134895716</t>
+  </si>
+  <si>
+    <t>134895715</t>
+  </si>
+  <si>
+    <t>134895808</t>
+  </si>
+  <si>
+    <t>134895912</t>
+  </si>
+  <si>
+    <t>134895984</t>
+  </si>
+  <si>
+    <t>134895941</t>
+  </si>
+  <si>
+    <t>134896025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 11.10.2025</t>
   </si>
 </sst>
 </file>
@@ -547,7 +583,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -785,7 +821,7 @@
       <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -819,7 +855,7 @@
       <c r="C15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -904,7 +940,7 @@
       <c r="C20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -972,7 +1008,7 @@
       <c r="C24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -987,12 +1023,182 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1010,31 +1216,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E2731-8597-4FBE-96B9-CCB1E1A10ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF91B384-453C-47AE-85C9-9EEA9B5C2262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="88">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,118 +65,244 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 10.10.2025</t>
-  </si>
-  <si>
-    <t>134873797</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 10.10.2025</t>
-  </si>
-  <si>
-    <t>134874162</t>
-  </si>
-  <si>
-    <t>134877198</t>
-  </si>
-  <si>
-    <t>134878394</t>
-  </si>
-  <si>
-    <t>134879442</t>
-  </si>
-  <si>
-    <t>134879919</t>
-  </si>
-  <si>
-    <t>134880048</t>
-  </si>
-  <si>
-    <t>134881500</t>
-  </si>
-  <si>
-    <t>134888999</t>
-  </si>
-  <si>
-    <t>134885230</t>
-  </si>
-  <si>
-    <t>134886317</t>
-  </si>
-  <si>
-    <t>134891167</t>
-  </si>
-  <si>
-    <t>134888267</t>
-  </si>
-  <si>
-    <t>134892347</t>
-  </si>
-  <si>
-    <t>134889893</t>
-  </si>
-  <si>
-    <t>134889595</t>
-  </si>
-  <si>
-    <t>134891290</t>
-  </si>
-  <si>
-    <t>134890153</t>
-  </si>
-  <si>
-    <t>134893153</t>
-  </si>
-  <si>
-    <t>134873786</t>
-  </si>
-  <si>
-    <t>134873890</t>
-  </si>
-  <si>
-    <t>134874875</t>
-  </si>
-  <si>
-    <t>134883895</t>
-  </si>
-  <si>
-    <t>134895479</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 11.10.2025</t>
-  </si>
-  <si>
-    <t>134895584</t>
-  </si>
-  <si>
-    <t>134895652</t>
-  </si>
-  <si>
-    <t>134895603</t>
-  </si>
-  <si>
-    <t>134895716</t>
-  </si>
-  <si>
-    <t>134895715</t>
-  </si>
-  <si>
-    <t>134895808</t>
-  </si>
-  <si>
-    <t>134895912</t>
-  </si>
-  <si>
-    <t>134895984</t>
-  </si>
-  <si>
-    <t>134895941</t>
-  </si>
-  <si>
-    <t>134896025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 11.10.2025</t>
+    <t>134938253</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 15.10.2025</t>
+  </si>
+  <si>
+    <t>134938318</t>
+  </si>
+  <si>
+    <t>134938608</t>
+  </si>
+  <si>
+    <t>134938803</t>
+  </si>
+  <si>
+    <t>134939208</t>
+  </si>
+  <si>
+    <t>134944195</t>
+  </si>
+  <si>
+    <t>134942683</t>
+  </si>
+  <si>
+    <t>134942711</t>
+  </si>
+  <si>
+    <t>134947450</t>
+  </si>
+  <si>
+    <t>134947807</t>
+  </si>
+  <si>
+    <t>134943188</t>
+  </si>
+  <si>
+    <t>134944181</t>
+  </si>
+  <si>
+    <t>134944010</t>
+  </si>
+  <si>
+    <t>134945141</t>
+  </si>
+  <si>
+    <t>134949870</t>
+  </si>
+  <si>
+    <t>134946277</t>
+  </si>
+  <si>
+    <t>134946691</t>
+  </si>
+  <si>
+    <t>134947250</t>
+  </si>
+  <si>
+    <t>134949508</t>
+  </si>
+  <si>
+    <t>134948743</t>
+  </si>
+  <si>
+    <t>134950604</t>
+  </si>
+  <si>
+    <t>134950861</t>
+  </si>
+  <si>
+    <t>134951128</t>
+  </si>
+  <si>
+    <t>134952023</t>
+  </si>
+  <si>
+    <t>134955595</t>
+  </si>
+  <si>
+    <t>134955837</t>
+  </si>
+  <si>
+    <t>134954218</t>
+  </si>
+  <si>
+    <t>134954363</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 15.10.2025</t>
+  </si>
+  <si>
+    <t>134961638</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 16.10.2025</t>
+  </si>
+  <si>
+    <t>134963579</t>
+  </si>
+  <si>
+    <t>134976632</t>
+  </si>
+  <si>
+    <t>134968722</t>
+  </si>
+  <si>
+    <t>134970387</t>
+  </si>
+  <si>
+    <t>134970415</t>
+  </si>
+  <si>
+    <t>134972856</t>
+  </si>
+  <si>
+    <t>134973966</t>
+  </si>
+  <si>
+    <t>134974969</t>
+  </si>
+  <si>
+    <t>134975417</t>
+  </si>
+  <si>
+    <t>134976175</t>
+  </si>
+  <si>
+    <t>134976518</t>
+  </si>
+  <si>
+    <t>134959072</t>
+  </si>
+  <si>
+    <t>134959850</t>
+  </si>
+  <si>
+    <t>134966829</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 16.10.2025</t>
+  </si>
+  <si>
+    <t>134930841</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 14.10.2025</t>
+  </si>
+  <si>
+    <t>134916601</t>
+  </si>
+  <si>
+    <t>134917196</t>
+  </si>
+  <si>
+    <t>134917346</t>
+  </si>
+  <si>
+    <t>134917933</t>
+  </si>
+  <si>
+    <t>134918172</t>
+  </si>
+  <si>
+    <t>134927008</t>
+  </si>
+  <si>
+    <t>134918482</t>
+  </si>
+  <si>
+    <t>134921315</t>
+  </si>
+  <si>
+    <t>134925400</t>
+  </si>
+  <si>
+    <t>134927435</t>
+  </si>
+  <si>
+    <t>134920779</t>
+  </si>
+  <si>
+    <t>134920579</t>
+  </si>
+  <si>
+    <t>134921402</t>
+  </si>
+  <si>
+    <t>131629873</t>
+  </si>
+  <si>
+    <t>134921767</t>
+  </si>
+  <si>
+    <t>134928190</t>
+  </si>
+  <si>
+    <t>134926532</t>
+  </si>
+  <si>
+    <t>134924470</t>
+  </si>
+  <si>
+    <t>134926482</t>
+  </si>
+  <si>
+    <t>134931227</t>
+  </si>
+  <si>
+    <t>134926446</t>
+  </si>
+  <si>
+    <t>134930289</t>
+  </si>
+  <si>
+    <t>134929387</t>
+  </si>
+  <si>
+    <t>134929884</t>
+  </si>
+  <si>
+    <t>134930352</t>
+  </si>
+  <si>
+    <t>134933764</t>
+  </si>
+  <si>
+    <t>134935399</t>
+  </si>
+  <si>
+    <t>134934426</t>
+  </si>
+  <si>
+    <t>134934933</t>
+  </si>
+  <si>
+    <t>134916675</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 14.10.2025</t>
   </si>
 </sst>
 </file>
@@ -583,7 +709,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -615,16 +741,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -633,16 +759,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -651,16 +777,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -669,16 +795,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -687,16 +813,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -705,16 +831,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -723,16 +849,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -741,16 +867,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -759,16 +885,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -777,16 +903,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -795,16 +921,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -813,16 +939,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -830,16 +956,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -847,16 +973,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -864,16 +990,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -881,16 +1007,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -898,16 +1024,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -915,16 +1041,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -932,16 +1058,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -949,16 +1075,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -966,16 +1092,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -983,16 +1109,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -1000,16 +1126,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -1017,16 +1143,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
@@ -1034,16 +1160,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -1051,16 +1177,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>5</v>
@@ -1068,16 +1194,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>5</v>
@@ -1085,16 +1211,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>9</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>5</v>
@@ -1102,16 +1228,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
@@ -1125,10 +1251,10 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>5</v>
@@ -1142,10 +1268,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>5</v>
@@ -1159,10 +1285,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>5</v>
@@ -1176,10 +1302,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>5</v>
@@ -1193,12 +1319,692 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7B5D03-BB56-4560-ACAB-07E766CDFC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8FC7A2-624D-4017-8CE9-297168C8D494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -68,91 +68,13 @@
     <t>Bloqueios Honda 15.10.2025</t>
   </si>
   <si>
-    <t>134961638</t>
-  </si>
-  <si>
     <t>Bloqueios Honda 16.10.2025</t>
   </si>
   <si>
-    <t>134963579</t>
-  </si>
-  <si>
-    <t>134976632</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 20.10.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 20.10.2025</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 18.10.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 18.10.2025</t>
-  </si>
-  <si>
-    <t>134979891</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 17.10.2025</t>
-  </si>
-  <si>
-    <t>134979765</t>
-  </si>
-  <si>
-    <t>134981700</t>
-  </si>
-  <si>
-    <t>134982516</t>
-  </si>
-  <si>
-    <t>134983652</t>
-  </si>
-  <si>
-    <t>134988599</t>
-  </si>
-  <si>
-    <t>134990659</t>
-  </si>
-  <si>
-    <t>134990848</t>
-  </si>
-  <si>
-    <t>134992384</t>
-  </si>
-  <si>
-    <t>134995464</t>
-  </si>
-  <si>
-    <t>134999338</t>
-  </si>
-  <si>
-    <t>134999773</t>
-  </si>
-  <si>
-    <t>135001185</t>
-  </si>
-  <si>
-    <t>134999165</t>
-  </si>
-  <si>
-    <t>134999251</t>
-  </si>
-  <si>
-    <t>135000418</t>
-  </si>
-  <si>
-    <t>134984933</t>
-  </si>
-  <si>
-    <t>134988928</t>
-  </si>
-  <si>
-    <t>134995529</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 17.10.2025</t>
+    <t>Bloqueios Honda 21.10.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 21.10.2025</t>
   </si>
 </sst>
 </file>
@@ -584,7 +506,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -622,10 +544,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -643,7 +565,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -661,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -670,16 +592,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>135008391</v>
+        <v>135021861</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -688,16 +610,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>135006688</v>
+        <v>135022426</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -706,16 +628,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>135007482</v>
+        <v>135035958</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -724,16 +646,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>135011847</v>
+        <v>135023541</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -742,16 +664,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
-        <v>135014311</v>
+        <v>135024558</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -760,16 +682,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>135014577</v>
+        <v>135024235</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -778,16 +700,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>135015496</v>
+        <v>135030440</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -796,16 +718,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>135016329</v>
+        <v>135026400</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -814,16 +736,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
-        <v>135016572</v>
+        <v>135027423</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -831,16 +753,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>135017014</v>
+        <v>135026975</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -848,16 +770,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>135017569</v>
+        <v>135027112</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -865,16 +787,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>135019725</v>
+        <v>135027109</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -882,16 +804,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <v>135019035</v>
+        <v>135028923</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -899,16 +821,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <v>135019494</v>
+        <v>135027929</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -916,16 +838,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <v>135005173</v>
+        <v>135029520</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -933,16 +855,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <v>135008078</v>
+        <v>135029174</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -950,16 +872,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <v>135011642</v>
+        <v>135029855</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -967,7 +889,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>134961638</v>
+        <v>135035021</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>7</v>
@@ -976,7 +898,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -984,16 +906,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
-        <v>134963579</v>
+        <v>135036541</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -1001,16 +923,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
-        <v>134976632</v>
+        <v>135038814</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -1018,16 +940,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
-        <v>135002233</v>
+        <v>135040436</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
@@ -1035,16 +957,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
-        <v>135002548</v>
+        <v>135040416</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -1052,16 +974,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
-        <v>135002346</v>
+        <v>135040614</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>5</v>
@@ -1069,16 +991,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
-        <v>133266532</v>
+        <v>135041119</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>5</v>
@@ -1086,16 +1008,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
-        <v>135002488</v>
+        <v>131542959</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>5</v>
@@ -1103,443 +1025,18 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
-        <v>135002743</v>
+        <v>135024300</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
-        <v>135002653</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
-        <v>135003045</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
-        <v>135002960</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E55" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1557,31 +1054,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8FC7A2-624D-4017-8CE9-297168C8D494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BBA33B-B645-4E27-B9D1-6D2B928A2967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -62,19 +62,16 @@
     <t>BLOQUEIOS HONDA 24.09.2025</t>
   </si>
   <si>
+    <t>BLOQUEIOS HONDA 21.10.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 22.10.2025</t>
+  </si>
+  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 15.10.2025</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 16.10.2025</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 21.10.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 21.10.2025</t>
+    <t>Bloqueios Honda 22.10.2025</t>
   </si>
 </sst>
 </file>
@@ -538,16 +535,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>134961638</v>
+        <v>135043255</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -556,16 +553,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>134963579</v>
+        <v>135043279</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -574,16 +571,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
-        <v>134976632</v>
+        <v>135043122</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -592,16 +589,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>135021861</v>
+        <v>135045951</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -610,16 +607,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>135022426</v>
+        <v>135045704</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -628,16 +625,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>135035958</v>
+        <v>135046890</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -646,16 +643,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>135023541</v>
+        <v>135049972</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -664,16 +661,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
-        <v>135024558</v>
+        <v>135051364</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -682,16 +679,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>135024235</v>
+        <v>135052822</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -700,16 +697,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>135030440</v>
+        <v>135053584</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -718,16 +715,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>135026400</v>
+        <v>135054476</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -736,16 +733,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
-        <v>135027423</v>
+        <v>135055674</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>11</v>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -753,16 +750,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>135026975</v>
+        <v>135056376</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -770,16 +767,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>135027112</v>
+        <v>135057939</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -787,16 +784,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>135027109</v>
+        <v>135059969</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -804,16 +801,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <v>135028923</v>
+        <v>135060163</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>11</v>
+      <c r="D17" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -821,224 +818,81 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <v>135027929</v>
+        <v>135060713</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
-        <v>135029520</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
-        <v>135029174</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>135029855</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
-        <v>135035021</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A22" s="10"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
-        <v>135036541</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A23" s="10"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
-        <v>135038814</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A24" s="10"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
-        <v>135040436</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
-        <v>135040416</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
-        <v>135040614</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
-        <v>135041119</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
-        <v>131542959</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
-        <v>135024300</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BBA33B-B645-4E27-B9D1-6D2B928A2967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705AF309-5CC2-4F61-9A59-F10D915DEC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -62,16 +62,13 @@
     <t>BLOQUEIOS HONDA 24.09.2025</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 21.10.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 22.10.2025</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 22.10.2025</t>
+    <t>Bloqueios Honda 23.10.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 23.10.2025</t>
   </si>
 </sst>
 </file>
@@ -535,16 +532,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>135043255</v>
+        <v>135065191</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -553,16 +550,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>135043279</v>
+        <v>135066509</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -571,16 +568,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
-        <v>135043122</v>
+        <v>135066526</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -589,16 +586,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>135045951</v>
+        <v>135068624</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -607,16 +604,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>135045704</v>
+        <v>135068867</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -625,16 +622,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>135046890</v>
+        <v>135073826</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -643,16 +640,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>135049972</v>
+        <v>135075194</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -661,16 +658,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
-        <v>135051364</v>
+        <v>135076377</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -679,16 +676,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>135052822</v>
+        <v>135076541</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -697,16 +694,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>135053584</v>
+        <v>135076907</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -715,16 +712,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>135054476</v>
+        <v>135078742</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -733,16 +730,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
-        <v>135055674</v>
+        <v>135079170</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -750,16 +747,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>135056376</v>
+        <v>135079857</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -767,16 +764,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>135057939</v>
+        <v>135062399</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -784,16 +781,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>135059969</v>
+        <v>135063139</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -801,16 +798,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <v>135060163</v>
+        <v>135067261</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -818,55 +815,139 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <v>135060713</v>
+        <v>132086660</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="9">
+        <v>135064871</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="9">
+        <v>135065844</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="9">
+        <v>135069708</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="10">
+        <v>135068363</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="10">
+        <v>135070042</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="10">
+        <v>135072377</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="9">
+        <v>135076464</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
@@ -908,31 +989,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705AF309-5CC2-4F61-9A59-F10D915DEC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA007F2-B5AF-42BA-BCE1-2938CEE0A13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,10 +65,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>Bloqueios Honda 23.10.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 23.10.2025</t>
+    <t>BLOQUEIOS HONDA 25.10.2025</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 25.10.2025</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 24.10.2025</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 24.10.2025</t>
   </si>
 </sst>
 </file>
@@ -532,16 +538,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>135065191</v>
+        <v>135105235</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -550,16 +556,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>135066509</v>
+        <v>135105703</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -568,16 +574,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
-        <v>135066526</v>
+        <v>135105268</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -586,16 +592,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>135068624</v>
+        <v>135085759</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -604,16 +610,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>135068867</v>
+        <v>135098754</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -622,16 +628,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>135073826</v>
+        <v>135088745</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -640,16 +646,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>135075194</v>
+        <v>135091576</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -658,16 +664,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
-        <v>135076377</v>
+        <v>135089466</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -676,16 +682,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>135076541</v>
+        <v>135094954</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -694,16 +700,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>135076907</v>
+        <v>135093068</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -712,16 +718,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>135078742</v>
+        <v>135093074</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -730,16 +736,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
-        <v>135079170</v>
+        <v>135093332</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -747,16 +753,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>135079857</v>
+        <v>135095525</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -764,16 +770,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>135062399</v>
+        <v>135096602</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -781,16 +787,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>135063139</v>
+        <v>135097482</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -798,16 +804,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <v>135067261</v>
+        <v>135100059</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -815,16 +821,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <v>132086660</v>
+        <v>135099238</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -832,16 +838,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <v>135064871</v>
+        <v>135099460</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -849,16 +855,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <v>135065844</v>
+        <v>135100097</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -866,16 +872,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <v>135069708</v>
+        <v>135100978</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -883,16 +889,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>135068363</v>
+        <v>135101068</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -900,16 +906,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
-        <v>135070042</v>
+        <v>135102154</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -917,16 +923,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
-        <v>135072377</v>
+        <v>135102987</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -934,31 +940,40 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
-        <v>135076464</v>
+        <v>135084532</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="6"/>
+      <c r="A26" s="9">
+        <v>135090962</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
+      <c r="D27" s="6"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
@@ -969,11 +984,13 @@
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="9"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="9"/>
+      <c r="D30" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA007F2-B5AF-42BA-BCE1-2938CEE0A13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF84B81D-0959-4764-BF92-275F0CAB14FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -65,16 +65,10 @@
     <t>971</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 25.10.2025</t>
+    <t>Bloqueios Honda 27.10.2025</t>
   </si>
   <si>
-    <t>Bloqueios Honda 25.10.2025</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 24.10.2025</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 24.10.2025</t>
+    <t>BLOQUEIOS HONDA 27.10.2025</t>
   </si>
 </sst>
 </file>
@@ -538,16 +532,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>135105235</v>
+        <v>135107753</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -556,16 +550,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>135105703</v>
+        <v>135107899</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -574,16 +568,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
-        <v>135105268</v>
+        <v>135108509</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -592,16 +586,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>135085759</v>
+        <v>135111898</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -610,16 +604,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>135098754</v>
+        <v>135111238</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -628,16 +622,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>135088745</v>
+        <v>135122977</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -646,16 +640,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>135091576</v>
+        <v>135115108</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -664,16 +658,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
-        <v>135089466</v>
+        <v>135116803</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -682,16 +676,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>135094954</v>
+        <v>135115386</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -700,16 +694,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>135093068</v>
+        <v>135115503</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -718,16 +712,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>135093074</v>
+        <v>135122036</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -736,16 +730,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
-        <v>135093332</v>
+        <v>135119301</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -753,16 +747,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>135095525</v>
+        <v>135119758</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -770,16 +764,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>135096602</v>
+        <v>135120194</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -787,16 +781,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>135097482</v>
+        <v>135120998</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -804,16 +798,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <v>135100059</v>
+        <v>135121252</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -821,16 +815,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <v>135099238</v>
+        <v>135121086</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -838,16 +832,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <v>135099460</v>
+        <v>135122286</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -855,16 +849,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <v>135100097</v>
+        <v>135123403</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -872,102 +866,50 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <v>135100978</v>
+        <v>135121481</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
-        <v>135101068</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A22" s="10"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
-        <v>135102154</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A23" s="10"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
-        <v>135102987</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A24" s="10"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
-        <v>135084532</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
-        <v>135090962</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
@@ -1006,31 +948,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{B579AA6C-A51F-4F2F-924D-03C29D31DE91}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21761C3-3D53-41DA-A4B3-A5CB55CEA215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
+    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,66 +54,83 @@
     <t>971</t>
   </si>
   <si>
-    <t>134810873</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 07.10.2025</t>
-  </si>
-  <si>
-    <t>134811463</t>
-  </si>
-  <si>
-    <t>134811627</t>
-  </si>
-  <si>
-    <t>134812122</t>
-  </si>
-  <si>
-    <t>134815536</t>
-  </si>
-  <si>
-    <t>134816289</t>
-  </si>
-  <si>
-    <t>134818715</t>
-  </si>
-  <si>
-    <t>134819364</t>
-  </si>
-  <si>
-    <t>134825211</t>
-  </si>
-  <si>
-    <t>134827591</t>
-  </si>
-  <si>
-    <t>134826981</t>
-  </si>
-  <si>
-    <t>134827573</t>
-  </si>
-  <si>
-    <t>134828602</t>
-  </si>
-  <si>
-    <t>134826810</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 07.10.2025</t>
-  </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; BLOQUEIOS HONDA 07.10.2025.xlsx.</t>
+    <t>135917392</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda  18.12.2025</t>
+  </si>
+  <si>
+    <t>135925443</t>
+  </si>
+  <si>
+    <t>135918336</t>
+  </si>
+  <si>
+    <t>135919097</t>
+  </si>
+  <si>
+    <t>135919112</t>
+  </si>
+  <si>
+    <t>135919415</t>
+  </si>
+  <si>
+    <t>135920859</t>
+  </si>
+  <si>
+    <t>135921741</t>
+  </si>
+  <si>
+    <t>135923858</t>
+  </si>
+  <si>
+    <t>135923596</t>
+  </si>
+  <si>
+    <t>135924848</t>
+  </si>
+  <si>
+    <t>135927788</t>
+  </si>
+  <si>
+    <t>135929066</t>
+  </si>
+  <si>
+    <t>135939272</t>
+  </si>
+  <si>
+    <t>135936745</t>
+  </si>
+  <si>
+    <t>135932647</t>
+  </si>
+  <si>
+    <t>135933471</t>
+  </si>
+  <si>
+    <t>135934470</t>
+  </si>
+  <si>
+    <t>135937568</t>
+  </si>
+  <si>
+    <t>135928278</t>
+  </si>
+  <si>
+    <t>135931529</t>
+  </si>
+  <si>
+    <t>135932258</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 18.12.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,14 +148,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -174,34 +183,31 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -218,10 +224,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -256,7 +262,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -308,7 +314,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -419,21 +425,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -450,7 +456,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -502,25 +508,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
-    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
-    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -554,14 +560,12 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -574,14 +578,12 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -594,14 +596,12 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -614,14 +614,12 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -634,14 +632,12 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -654,14 +650,12 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -670,18 +664,16 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -694,14 +686,12 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -714,14 +704,12 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -734,14 +722,12 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -754,14 +740,12 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -774,14 +758,12 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -794,14 +776,12 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" t="s">
-        <v>25</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -814,81 +794,194 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F15" t="s">
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F24"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_Bloqueios_Honda.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21761C3-3D53-41DA-A4B3-A5CB55CEA215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{F687C37F-93E0-43D5-B61D-2BD48107E6AD}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
+    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,82 +54,35 @@
     <t>971</t>
   </si>
   <si>
-    <t>135917392</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda  18.12.2025</t>
-  </si>
-  <si>
-    <t>135925443</t>
-  </si>
-  <si>
-    <t>135918336</t>
-  </si>
-  <si>
-    <t>135919097</t>
-  </si>
-  <si>
-    <t>135919112</t>
-  </si>
-  <si>
-    <t>135919415</t>
-  </si>
-  <si>
-    <t>135920859</t>
-  </si>
-  <si>
-    <t>135921741</t>
-  </si>
-  <si>
-    <t>135923858</t>
-  </si>
-  <si>
-    <t>135923596</t>
-  </si>
-  <si>
-    <t>135924848</t>
-  </si>
-  <si>
-    <t>135927788</t>
-  </si>
-  <si>
-    <t>135929066</t>
-  </si>
-  <si>
-    <t>135939272</t>
-  </si>
-  <si>
-    <t>135936745</t>
-  </si>
-  <si>
-    <t>135932647</t>
-  </si>
-  <si>
-    <t>135933471</t>
-  </si>
-  <si>
-    <t>135934470</t>
-  </si>
-  <si>
-    <t>135937568</t>
-  </si>
-  <si>
-    <t>135928278</t>
-  </si>
-  <si>
-    <t>135931529</t>
-  </si>
-  <si>
-    <t>135932258</t>
-  </si>
-  <si>
-    <t>BLOQUEIOS HONDA 18.12.2025</t>
+    <t>141164515</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 01.10.2026</t>
+  </si>
+  <si>
+    <t>141167479</t>
+  </si>
+  <si>
+    <t>141164718</t>
+  </si>
+  <si>
+    <t>141168317</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 01.10.2026</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; BLOQUEIOS HONDA 01.10.2026.xlsx.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -183,31 +136,31 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -224,10 +177,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -262,7 +215,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -314,7 +267,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -425,21 +378,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -456,7 +409,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -508,25 +461,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
+    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
+    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -560,12 +513,14 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2"/>
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -578,12 +533,14 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3"/>
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -596,12 +553,14 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4"/>
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -614,344 +573,24 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="F5" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
